--- a/archivos_listados.xlsx
+++ b/archivos_listados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B126"/>
+  <dimension ref="A1:B696"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,1500 +443,8340 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DSC_0240.jpg</t>
+          <t>DSC_0103.jpg</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>'DSC_0240.jpg',</t>
+          <t>'DSC_0103.jpg',</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DSC_0241.jpg</t>
+          <t>DSC_0104.jpg</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>'DSC_0241.jpg',</t>
+          <t>'DSC_0104.jpg',</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DSC_0244.jpg</t>
+          <t>DSC_0105.jpg</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>'DSC_0244.jpg',</t>
+          <t>'DSC_0105.jpg',</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DSC_0245.jpg</t>
+          <t>DSC_0106.jpg</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>'DSC_0245.jpg',</t>
+          <t>'DSC_0106.jpg',</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DSC_0248.jpg</t>
+          <t>DSC_0107.jpg</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>'DSC_0248.jpg',</t>
+          <t>'DSC_0107.jpg',</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DSC_0250.jpg</t>
+          <t>DSC_0108.jpg</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>'DSC_0250.jpg',</t>
+          <t>'DSC_0108.jpg',</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DSC_0252.jpg</t>
+          <t>DSC_0109.jpg</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>'DSC_0252.jpg',</t>
+          <t>'DSC_0109.jpg',</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DSC_0253.jpg</t>
+          <t>DSC_0110.jpg</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>'DSC_0253.jpg',</t>
+          <t>'DSC_0110.jpg',</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DSC_0255.jpg</t>
+          <t>DSC_0111.jpg</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>'DSC_0255.jpg',</t>
+          <t>'DSC_0111.jpg',</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DSC_0256.jpg</t>
+          <t>DSC_0112.jpg</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>'DSC_0256.jpg',</t>
+          <t>'DSC_0112.jpg',</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DSC_0257.jpg</t>
+          <t>DSC_0113.jpg</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>'DSC_0257.jpg',</t>
+          <t>'DSC_0113.jpg',</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DSC_0258.jpg</t>
+          <t>DSC_0114.jpg</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>'DSC_0258.jpg',</t>
+          <t>'DSC_0114.jpg',</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DSC_0259.jpg</t>
+          <t>DSC_0115.jpg</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>'DSC_0259.jpg',</t>
+          <t>'DSC_0115.jpg',</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DSC_0260.jpg</t>
+          <t>DSC_0116.jpg</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>'DSC_0260.jpg',</t>
+          <t>'DSC_0116.jpg',</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DSC_0262.jpg</t>
+          <t>DSC_0118.jpg</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>'DSC_0262.jpg',</t>
+          <t>'DSC_0118.jpg',</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DSC_0263.jpg</t>
+          <t>DSC_0119.jpg</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>'DSC_0263.jpg',</t>
+          <t>'DSC_0119.jpg',</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DSC_0264.jpg</t>
+          <t>DSC_0120.jpg</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>'DSC_0264.jpg',</t>
+          <t>'DSC_0120.jpg',</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DSC_0266.jpg</t>
+          <t>DSC_0121.jpg</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>'DSC_0266.jpg',</t>
+          <t>'DSC_0121.jpg',</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DSC_0267.jpg</t>
+          <t>DSC_0122.jpg</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>'DSC_0267.jpg',</t>
+          <t>'DSC_0122.jpg',</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DSC_0270.jpg</t>
+          <t>DSC_0123.jpg</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>'DSC_0270.jpg',</t>
+          <t>'DSC_0123.jpg',</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DSC_0273.jpg</t>
+          <t>DSC_0124.jpg</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>'DSC_0273.jpg',</t>
+          <t>'DSC_0124.jpg',</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DSC_0274.jpg</t>
+          <t>DSC_0125.jpg</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>'DSC_0274.jpg',</t>
+          <t>'DSC_0125.jpg',</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DSC_0276.jpg</t>
+          <t>DSC_0126.jpg</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>'DSC_0276.jpg',</t>
+          <t>'DSC_0126.jpg',</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DSC_0277.jpg</t>
+          <t>DSC_0127.jpg</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>'DSC_0277.jpg',</t>
+          <t>'DSC_0127.jpg',</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DSC_0278.jpg</t>
+          <t>DSC_0128.jpg</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>'DSC_0278.jpg',</t>
+          <t>'DSC_0128.jpg',</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DSC_0279.jpg</t>
+          <t>DSC_0129.jpg</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>'DSC_0279.jpg',</t>
+          <t>'DSC_0129.jpg',</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DSC_0280.jpg</t>
+          <t>DSC_0130.jpg</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>'DSC_0280.jpg',</t>
+          <t>'DSC_0130.jpg',</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DSC_0281.jpg</t>
+          <t>DSC_0131.jpg</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>'DSC_0281.jpg',</t>
+          <t>'DSC_0131.jpg',</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DSC_0282.jpg</t>
+          <t>DSC_0132.jpg</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>'DSC_0282.jpg',</t>
+          <t>'DSC_0132.jpg',</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DSC_0283.jpg</t>
+          <t>DSC_0144.jpg</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>'DSC_0283.jpg',</t>
+          <t>'DSC_0144.jpg',</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DSC_0284.jpg</t>
+          <t>DSC_0145.jpg</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>'DSC_0284.jpg',</t>
+          <t>'DSC_0145.jpg',</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DSC_0285.jpg</t>
+          <t>DSC_0146.jpg</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>'DSC_0285.jpg',</t>
+          <t>'DSC_0146.jpg',</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DSC_0286.jpg</t>
+          <t>DSC_0148.jpg</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>'DSC_0286.jpg',</t>
+          <t>'DSC_0148.jpg',</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DSC_0287.jpg</t>
+          <t>DSC_0149.jpg</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>'DSC_0287.jpg',</t>
+          <t>'DSC_0149.jpg',</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DSC_0288.jpg</t>
+          <t>DSC_0150.jpg</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>'DSC_0288.jpg',</t>
+          <t>'DSC_0150.jpg',</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DSC_0289.jpg</t>
+          <t>DSC_0151.jpg</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>'DSC_0289.jpg',</t>
+          <t>'DSC_0151.jpg',</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DSC_0290.jpg</t>
+          <t>DSC_0152.jpg</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>'DSC_0290.jpg',</t>
+          <t>'DSC_0152.jpg',</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DSC_0291.jpg</t>
+          <t>DSC_0154.jpg</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>'DSC_0291.jpg',</t>
+          <t>'DSC_0154.jpg',</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DSC_0292.jpg</t>
+          <t>DSC_0155.jpg</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>'DSC_0292.jpg',</t>
+          <t>'DSC_0155.jpg',</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DSC_0295.jpg</t>
+          <t>DSC_0156.jpg</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>'DSC_0295.jpg',</t>
+          <t>'DSC_0156.jpg',</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DSC_0297.jpg</t>
+          <t>DSC_0157.jpg</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>'DSC_0297.jpg',</t>
+          <t>'DSC_0157.jpg',</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DSC_0301.jpg</t>
+          <t>DSC_0158.jpg</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>'DSC_0301.jpg',</t>
+          <t>'DSC_0158.jpg',</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DSC_0302.jpg</t>
+          <t>DSC_0159.jpg</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>'DSC_0302.jpg',</t>
+          <t>'DSC_0159.jpg',</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DSC_0303.jpg</t>
+          <t>DSC_0160.jpg</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>'DSC_0303.jpg',</t>
+          <t>'DSC_0160.jpg',</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DSC_0304.jpg</t>
+          <t>DSC_0161.jpg</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>'DSC_0304.jpg',</t>
+          <t>'DSC_0161.jpg',</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DSC_0307.jpg</t>
+          <t>DSC_0162.jpg</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>'DSC_0307.jpg',</t>
+          <t>'DSC_0162.jpg',</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DSC_0310.jpg</t>
+          <t>DSC_0163.jpg</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>'DSC_0310.jpg',</t>
+          <t>'DSC_0163.jpg',</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DSC_0312.jpg</t>
+          <t>DSC_0164.jpg</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>'DSC_0312.jpg',</t>
+          <t>'DSC_0164.jpg',</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DSC_0313.jpg</t>
+          <t>DSC_0165.jpg</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>'DSC_0313.jpg',</t>
+          <t>'DSC_0165.jpg',</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DSC_0315.jpg</t>
+          <t>DSC_0166.jpg</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>'DSC_0315.jpg',</t>
+          <t>'DSC_0166.jpg',</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DSC_0316.jpg</t>
+          <t>DSC_0168.jpg</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>'DSC_0316.jpg',</t>
+          <t>'DSC_0168.jpg',</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DSC_0317.jpg</t>
+          <t>DSC_0169.jpg</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>'DSC_0317.jpg',</t>
+          <t>'DSC_0169.jpg',</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DSC_0318.jpg</t>
+          <t>DSC_0170.jpg</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>'DSC_0318.jpg',</t>
+          <t>'DSC_0170.jpg',</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DSC_0325.jpg</t>
+          <t>DSC_0172.jpg</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>'DSC_0325.jpg',</t>
+          <t>'DSC_0172.jpg',</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DSC_0326.jpg</t>
+          <t>DSC_0173.jpg</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>'DSC_0326.jpg',</t>
+          <t>'DSC_0173.jpg',</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DSC_0331.jpg</t>
+          <t>DSC_0174.jpg</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>'DSC_0331.jpg',</t>
+          <t>'DSC_0174.jpg',</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DSC_0332.jpg</t>
+          <t>DSC_0175.jpg</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>'DSC_0332.jpg',</t>
+          <t>'DSC_0175.jpg',</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DSC_0333.jpg</t>
+          <t>DSC_0176.jpg</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>'DSC_0333.jpg',</t>
+          <t>'DSC_0176.jpg',</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DSC_0334.jpg</t>
+          <t>DSC_0177.jpg</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>'DSC_0334.jpg',</t>
+          <t>'DSC_0177.jpg',</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DSC_0335.jpg</t>
+          <t>DSC_0179.jpg</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>'DSC_0335.jpg',</t>
+          <t>'DSC_0179.jpg',</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DSC_0338.jpg</t>
+          <t>DSC_0180.jpg</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>'DSC_0338.jpg',</t>
+          <t>'DSC_0180.jpg',</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DSC_0339.jpg</t>
+          <t>DSC_0182.jpg</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>'DSC_0339.jpg',</t>
+          <t>'DSC_0182.jpg',</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DSC_0340.jpg</t>
+          <t>DSC_0183.jpg</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>'DSC_0340.jpg',</t>
+          <t>'DSC_0183.jpg',</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DSC_0341.jpg</t>
+          <t>DSC_0184.jpg</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>'DSC_0341.jpg',</t>
+          <t>'DSC_0184.jpg',</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>DSC_0342.jpg</t>
+          <t>DSC_0185.jpg</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>'DSC_0342.jpg',</t>
+          <t>'DSC_0185.jpg',</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>DSC_0343.jpg</t>
+          <t>DSC_0186.jpg</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>'DSC_0343.jpg',</t>
+          <t>'DSC_0186.jpg',</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>DSC_0347.jpg</t>
+          <t>DSC_0187.jpg</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>'DSC_0347.jpg',</t>
+          <t>'DSC_0187.jpg',</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>DSC_0348.jpg</t>
+          <t>DSC_0188.jpg</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>'DSC_0348.jpg',</t>
+          <t>'DSC_0188.jpg',</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>DSC_0349.jpg</t>
+          <t>DSC_0190.jpg</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>'DSC_0349.jpg',</t>
+          <t>'DSC_0190.jpg',</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>DSC_0352.jpg</t>
+          <t>DSC_0191.jpg</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>'DSC_0352.jpg',</t>
+          <t>'DSC_0191.jpg',</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>DSC_0353.jpg</t>
+          <t>DSC_0192.jpg</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>'DSC_0353.jpg',</t>
+          <t>'DSC_0192.jpg',</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DSC_0355.jpg</t>
+          <t>DSC_0193.jpg</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>'DSC_0355.jpg',</t>
+          <t>'DSC_0193.jpg',</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>DSC_0356.jpg</t>
+          <t>DSC_0194.jpg</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>'DSC_0356.jpg',</t>
+          <t>'DSC_0194.jpg',</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DSC_0358.jpg</t>
+          <t>DSC_0195.jpg</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>'DSC_0358.jpg',</t>
+          <t>'DSC_0195.jpg',</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DSC_0359.jpg</t>
+          <t>DSC_0196.jpg</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>'DSC_0359.jpg',</t>
+          <t>'DSC_0196.jpg',</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DSC_0360.jpg</t>
+          <t>DSC_0197.jpg</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>'DSC_0360.jpg',</t>
+          <t>'DSC_0197.jpg',</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DSC_0362.jpg</t>
+          <t>DSC_0198.jpg</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>'DSC_0362.jpg',</t>
+          <t>'DSC_0198.jpg',</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>DSC_0363.jpg</t>
+          <t>DSC_0199.jpg</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>'DSC_0363.jpg',</t>
+          <t>'DSC_0199.jpg',</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>DSC_0364.jpg</t>
+          <t>DSC_0200.jpg</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>'DSC_0364.jpg',</t>
+          <t>'DSC_0200.jpg',</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>DSC_0365.jpg</t>
+          <t>DSC_0201.jpg</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>'DSC_0365.jpg',</t>
+          <t>'DSC_0201.jpg',</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>DSC_0367.jpg</t>
+          <t>DSC_0202.jpg</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>'DSC_0367.jpg',</t>
+          <t>'DSC_0202.jpg',</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>DSC_0368.jpg</t>
+          <t>DSC_0203.jpg</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>'DSC_0368.jpg',</t>
+          <t>'DSC_0203.jpg',</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>DSC_0369.jpg</t>
+          <t>DSC_0204.jpg</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>'DSC_0369.jpg',</t>
+          <t>'DSC_0204.jpg',</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>DSC_0371.jpg</t>
+          <t>DSC_0205.jpg</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>'DSC_0371.jpg',</t>
+          <t>'DSC_0205.jpg',</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DSC_0373.jpg</t>
+          <t>DSC_0206.jpg</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>'DSC_0373.jpg',</t>
+          <t>'DSC_0206.jpg',</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DSC_0374.jpg</t>
+          <t>DSC_0207.jpg</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>'DSC_0374.jpg',</t>
+          <t>'DSC_0207.jpg',</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DSC_0376.jpg</t>
+          <t>DSC_0208.jpg</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>'DSC_0376.jpg',</t>
+          <t>'DSC_0208.jpg',</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>DSC_0378.jpg</t>
+          <t>DSC_0209.jpg</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>'DSC_0378.jpg',</t>
+          <t>'DSC_0209.jpg',</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>DSC_0379.jpg</t>
+          <t>DSC_0210.jpg</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>'DSC_0379.jpg',</t>
+          <t>'DSC_0210.jpg',</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>DSC_0380.jpg</t>
+          <t>DSC_0211.jpg</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>'DSC_0380.jpg',</t>
+          <t>'DSC_0211.jpg',</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>DSC_0382.jpg</t>
+          <t>DSC_0212.jpg</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>'DSC_0382.jpg',</t>
+          <t>'DSC_0212.jpg',</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>DSC_0383.jpg</t>
+          <t>DSC_0213.jpg</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>'DSC_0383.jpg',</t>
+          <t>'DSC_0213.jpg',</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>DSC_0384.jpg</t>
+          <t>DSC_0214.jpg</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>'DSC_0384.jpg',</t>
+          <t>'DSC_0214.jpg',</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>DSC_0385.jpg</t>
+          <t>DSC_0215.jpg</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>'DSC_0385.jpg',</t>
+          <t>'DSC_0215.jpg',</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>DSC_0386.jpg</t>
+          <t>DSC_0216.jpg</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>'DSC_0386.jpg',</t>
+          <t>'DSC_0216.jpg',</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>DSC_0387.jpg</t>
+          <t>DSC_0218.jpg</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>'DSC_0387.jpg',</t>
+          <t>'DSC_0218.jpg',</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>DSC_0388.jpg</t>
+          <t>DSC_0219.jpg</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>'DSC_0388.jpg',</t>
+          <t>'DSC_0219.jpg',</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>DSC_0390.jpg</t>
+          <t>DSC_0220.jpg</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>'DSC_0390.jpg',</t>
+          <t>'DSC_0220.jpg',</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>DSC_0391.jpg</t>
+          <t>DSC_0221.jpg</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>'DSC_0391.jpg',</t>
+          <t>'DSC_0221.jpg',</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>DSC_0393.jpg</t>
+          <t>DSC_0222.jpg</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>'DSC_0393.jpg',</t>
+          <t>'DSC_0222.jpg',</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>DSC_0395.jpg</t>
+          <t>DSC_0224.jpg</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>'DSC_0395.jpg',</t>
+          <t>'DSC_0224.jpg',</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>DSC_0396.jpg</t>
+          <t>DSC_0226.jpg</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>'DSC_0396.jpg',</t>
+          <t>'DSC_0226.jpg',</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>DSC_0397.jpg</t>
+          <t>DSC_0227.jpg</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>'DSC_0397.jpg',</t>
+          <t>'DSC_0227.jpg',</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>DSC_0398.jpg</t>
+          <t>DSC_0228.jpg</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>'DSC_0398.jpg',</t>
+          <t>'DSC_0228.jpg',</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>DSC_0399.jpg</t>
+          <t>DSC_0229.jpg</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>'DSC_0399.jpg',</t>
+          <t>'DSC_0229.jpg',</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>DSC_0400.jpg</t>
+          <t>DSC_0230.jpg</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>'DSC_0400.jpg',</t>
+          <t>'DSC_0230.jpg',</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>DSC_0401.jpg</t>
+          <t>DSC_0231.jpg</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>'DSC_0401.jpg',</t>
+          <t>'DSC_0231.jpg',</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>DSC_0402.jpg</t>
+          <t>DSC_0232.jpg</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>'DSC_0402.jpg',</t>
+          <t>'DSC_0232.jpg',</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>DSC_0405.jpg</t>
+          <t>DSC_0233.jpg</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>'DSC_0405.jpg',</t>
+          <t>'DSC_0233.jpg',</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>DSC_0409.jpg</t>
+          <t>DSC_0234.jpg</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>'DSC_0409.jpg',</t>
+          <t>'DSC_0234.jpg',</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>DSC_0410.jpg</t>
+          <t>DSC_0235.jpg</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>'DSC_0410.jpg',</t>
+          <t>'DSC_0235.jpg',</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>DSC_0411.jpg</t>
+          <t>DSC_0236.jpg</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>'DSC_0411.jpg',</t>
+          <t>'DSC_0236.jpg',</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>DSC_0412.jpg</t>
+          <t>DSC_0237.jpg</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>'DSC_0412.jpg',</t>
+          <t>'DSC_0237.jpg',</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>DSC_0413.jpg</t>
+          <t>DSC_0238.jpg</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>'DSC_0413.jpg',</t>
+          <t>'DSC_0238.jpg',</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>DSC_0414.jpg</t>
+          <t>DSC_0239.jpg</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>'DSC_0414.jpg',</t>
+          <t>'DSC_0239.jpg',</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>DSC_0415.jpg</t>
+          <t>DSC_0240.jpg</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>'DSC_0415.jpg',</t>
+          <t>'DSC_0240.jpg',</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>DSC_0416.jpg</t>
+          <t>DSC_0241.jpg</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>'DSC_0416.jpg',</t>
+          <t>'DSC_0241.jpg',</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>DSC_0417.jpg</t>
+          <t>DSC_0242.jpg</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>'DSC_0417.jpg',</t>
+          <t>'DSC_0242.jpg',</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>DSC_0418.jpg</t>
+          <t>DSC_0243.jpg</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>'DSC_0418.jpg',</t>
+          <t>'DSC_0243.jpg',</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>DSC_0419.jpg</t>
+          <t>DSC_0244.jpg</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>'DSC_0419.jpg',</t>
+          <t>'DSC_0244.jpg',</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>DSC_0420.jpg</t>
+          <t>DSC_0245.jpg</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>'DSC_0420.jpg',</t>
+          <t>'DSC_0245.jpg',</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>DSC_0422.jpg</t>
+          <t>DSC_0247.jpg</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>'DSC_0422.jpg',</t>
+          <t>'DSC_0247.jpg',</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>DSC_0423.jpg</t>
+          <t>DSC_0248.jpg</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>'DSC_0423.jpg',</t>
+          <t>'DSC_0248.jpg',</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>DSC_0424.jpg</t>
+          <t>DSC_0249.jpg</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>'DSC_0424.jpg',</t>
+          <t>'DSC_0249.jpg',</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
+          <t>DSC_0251.jpg</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>'DSC_0251.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>DSC_0252.jpg</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>'DSC_0252.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>DSC_0254.jpg</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>'DSC_0254.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>DSC_0255.jpg</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>'DSC_0255.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>DSC_0256.jpg</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>'DSC_0256.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>DSC_0257.jpg</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>'DSC_0257.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>DSC_0258.jpg</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>'DSC_0258.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>DSC_0259.jpg</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>'DSC_0259.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>DSC_0260.jpg</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>'DSC_0260.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>DSC_0261.jpg</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>'DSC_0261.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>DSC_0263.jpg</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>'DSC_0263.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>DSC_0264.jpg</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>'DSC_0264.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>DSC_0265.jpg</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>'DSC_0265.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>DSC_0266.jpg</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>'DSC_0266.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>DSC_0267.jpg</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>'DSC_0267.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>DSC_0268.jpg</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>'DSC_0268.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>DSC_0269.jpg</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>'DSC_0269.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>DSC_0270.jpg</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>'DSC_0270.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>DSC_0271.jpg</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>'DSC_0271.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>DSC_0272.jpg</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>'DSC_0272.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>DSC_0273.jpg</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>'DSC_0273.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>DSC_0274.jpg</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>'DSC_0274.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>DSC_0275.jpg</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>'DSC_0275.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>DSC_0276.jpg</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>'DSC_0276.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>DSC_0277.jpg</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>'DSC_0277.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>DSC_0278.jpg</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>'DSC_0278.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>DSC_0279.jpg</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>'DSC_0279.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>DSC_0280.jpg</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>'DSC_0280.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>DSC_0281.jpg</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>'DSC_0281.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>DSC_0282.jpg</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>'DSC_0282.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>DSC_0283.jpg</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>'DSC_0283.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>DSC_0284.jpg</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>'DSC_0284.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>DSC_0288.jpg</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>'DSC_0288.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>DSC_0290.jpg</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>'DSC_0290.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>DSC_0291.jpg</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>'DSC_0291.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>DSC_0292.jpg</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>'DSC_0292.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>DSC_0293.jpg</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>'DSC_0293.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>DSC_0294.jpg</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>'DSC_0294.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>DSC_0295.jpg</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>'DSC_0295.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>DSC_0296.jpg</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>'DSC_0296.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>DSC_0297.jpg</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>'DSC_0297.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>DSC_0298.jpg</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>'DSC_0298.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>DSC_0300.jpg</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>'DSC_0300.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>DSC_0301.jpg</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>'DSC_0301.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>DSC_0302.jpg</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>'DSC_0302.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>DSC_0305.jpg</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>'DSC_0305.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>DSC_0306.jpg</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>'DSC_0306.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>DSC_0307.jpg</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>'DSC_0307.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>DSC_0310.jpg</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>'DSC_0310.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>DSC_0311.jpg</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>'DSC_0311.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>DSC_0312.jpg</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>'DSC_0312.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>DSC_0313.jpg</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>'DSC_0313.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>DSC_0314.jpg</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>'DSC_0314.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>DSC_0316.jpg</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>'DSC_0316.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>DSC_0317.jpg</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>'DSC_0317.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>DSC_0318.jpg</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>'DSC_0318.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>DSC_0319.jpg</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>'DSC_0319.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>DSC_0320.jpg</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>'DSC_0320.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>DSC_0321.jpg</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>'DSC_0321.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>DSC_0322.jpg</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>'DSC_0322.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>DSC_0323.jpg</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>'DSC_0323.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>DSC_0327.jpg</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>'DSC_0327.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>DSC_0328.jpg</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>'DSC_0328.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>DSC_0329.jpg</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>'DSC_0329.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>DSC_0330.jpg</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>'DSC_0330.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>DSC_0331.jpg</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>'DSC_0331.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>DSC_0332.jpg</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>'DSC_0332.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>DSC_0337.jpg</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>'DSC_0337.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>DSC_0338.jpg</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>'DSC_0338.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>DSC_0339.jpg</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>'DSC_0339.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>DSC_0340.jpg</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>'DSC_0340.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>DSC_0341.jpg</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>'DSC_0341.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>DSC_0342.jpg</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>'DSC_0342.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>DSC_0343.jpg</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>'DSC_0343.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>DSC_0347.jpg</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>'DSC_0347.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>DSC_0350.jpg</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>'DSC_0350.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>DSC_0351.jpg</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>'DSC_0351.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>DSC_0352.jpg</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>'DSC_0352.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>DSC_0353.jpg</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>'DSC_0353.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>DSC_0354.jpg</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>'DSC_0354.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>DSC_0357.jpg</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>'DSC_0357.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>DSC_0358.jpg</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>'DSC_0358.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>DSC_0359.jpg</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>'DSC_0359.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>DSC_0360.jpg</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>'DSC_0360.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>DSC_0361.jpg</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>'DSC_0361.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>DSC_0363.jpg</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>'DSC_0363.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>DSC_0364.jpg</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>'DSC_0364.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>DSC_0365.jpg</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>'DSC_0365.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>DSC_0366.jpg</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>'DSC_0366.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>DSC_0367.jpg</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>'DSC_0367.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>DSC_0368.jpg</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>'DSC_0368.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>DSC_0369.jpg</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>'DSC_0369.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>DSC_0370.jpg</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>'DSC_0370.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>DSC_0371.jpg</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>'DSC_0371.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>DSC_0372.jpg</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>'DSC_0372.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>DSC_0373.jpg</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>'DSC_0373.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>DSC_0375.jpg</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>'DSC_0375.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>DSC_0376.jpg</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>'DSC_0376.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>DSC_0377.jpg</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>'DSC_0377.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>DSC_0378.jpg</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>'DSC_0378.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>DSC_0379.jpg</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>'DSC_0379.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>DSC_0380.jpg</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>'DSC_0380.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>DSC_0381.jpg</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>'DSC_0381.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>DSC_0385.jpg</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>'DSC_0385.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>DSC_0386.jpg</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>'DSC_0386.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>DSC_0387.jpg</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>'DSC_0387.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>DSC_0388.jpg</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>'DSC_0388.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>DSC_0389.jpg</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>'DSC_0389.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>DSC_0390.jpg</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>'DSC_0390.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>DSC_0392.jpg</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>'DSC_0392.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>DSC_0393.jpg</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>'DSC_0393.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>DSC_0396.jpg</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>'DSC_0396.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>DSC_0399.jpg</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>'DSC_0399.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>DSC_0400.jpg</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>'DSC_0400.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>DSC_0401.jpg</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>'DSC_0401.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>DSC_0402.jpg</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>'DSC_0402.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>DSC_0404.jpg</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>'DSC_0404.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>DSC_0405.jpg</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>'DSC_0405.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>DSC_0406.jpg</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>'DSC_0406.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>DSC_0407.jpg</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>'DSC_0407.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>DSC_0409.jpg</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>'DSC_0409.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>DSC_0410.jpg</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>'DSC_0410.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>DSC_0411.jpg</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>'DSC_0411.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>DSC_0412.jpg</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>'DSC_0412.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>DSC_0413.jpg</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>'DSC_0413.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>DSC_0414.jpg</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>'DSC_0414.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>DSC_0415.jpg</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>'DSC_0415.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>DSC_0416.jpg</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>'DSC_0416.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>DSC_0417.jpg</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>'DSC_0417.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>DSC_0418.jpg</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>'DSC_0418.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>DSC_0419.jpg</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>'DSC_0419.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>DSC_0420.jpg</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>'DSC_0420.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>DSC_0423.jpg</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>'DSC_0423.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>DSC_0424.jpg</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>'DSC_0424.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
           <t>DSC_0425.jpg</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
+      <c r="B260" t="inlineStr">
         <is>
           <t>'DSC_0425.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>DSC_0426.jpg</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>'DSC_0426.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>DSC_0427.jpg</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>'DSC_0427.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>DSC_0428.jpg</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>'DSC_0428.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>DSC_0429.jpg</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>'DSC_0429.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>DSC_0430.jpg</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>'DSC_0430.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>DSC_0431.jpg</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>'DSC_0431.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>DSC_0432.jpg</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>'DSC_0432.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>DSC_0433.jpg</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>'DSC_0433.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>DSC_0434.jpg</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>'DSC_0434.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>DSC_0435.jpg</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>'DSC_0435.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>DSC_0436.jpg</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>'DSC_0436.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>DSC_0437.jpg</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>'DSC_0437.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>DSC_0439.jpg</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>'DSC_0439.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>DSC_0442.jpg</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>'DSC_0442.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>DSC_0443.jpg</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>'DSC_0443.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>DSC_0444.jpg</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>'DSC_0444.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>DSC_0445.jpg</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>'DSC_0445.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>DSC_0446.jpg</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>'DSC_0446.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>DSC_0448.jpg</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>'DSC_0448.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>DSC_0449.jpg</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>'DSC_0449.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>DSC_0450.jpg</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>'DSC_0450.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>DSC_0451.jpg</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>'DSC_0451.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>DSC_0452.jpg</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>'DSC_0452.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>DSC_0453.jpg</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>'DSC_0453.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>DSC_0454.jpg</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>'DSC_0454.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>DSC_0455.jpg</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>'DSC_0455.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>DSC_0457.jpg</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>'DSC_0457.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>DSC_0458.jpg</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>'DSC_0458.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>DSC_0459.jpg</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>'DSC_0459.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>DSC_0460.jpg</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>'DSC_0460.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>DSC_0461.jpg</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>'DSC_0461.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>DSC_0462.jpg</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>'DSC_0462.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>DSC_0463.jpg</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>'DSC_0463.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>DSC_0464.jpg</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>'DSC_0464.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>DSC_0465.jpg</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>'DSC_0465.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>DSC_0466.jpg</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>'DSC_0466.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>DSC_0467.jpg</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>'DSC_0467.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>DSC_0468.jpg</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>'DSC_0468.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>DSC_0469.jpg</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>'DSC_0469.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>DSC_0473.jpg</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>'DSC_0473.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>DSC_0476.jpg</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>'DSC_0476.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>DSC_0477.jpg</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>'DSC_0477.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>DSC_0478.jpg</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>'DSC_0478.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>DSC_0479.jpg</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>'DSC_0479.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>DSC_0480.jpg</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>'DSC_0480.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>DSC_0483.jpg</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>'DSC_0483.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>DSC_0485.jpg</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>'DSC_0485.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>DSC_0486.jpg</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>'DSC_0486.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>DSC_0487.jpg</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>'DSC_0487.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>DSC_0488.jpg</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>'DSC_0488.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>DSC_0490.jpg</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>'DSC_0490.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>DSC_0491.jpg</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>'DSC_0491.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>DSC_0494.jpg</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>'DSC_0494.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>DSC_0496.jpg</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>'DSC_0496.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>DSC_0497.jpg</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>'DSC_0497.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>DSC_0498.jpg</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>'DSC_0498.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>DSC_0499.jpg</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>'DSC_0499.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>DSC_0500.jpg</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>'DSC_0500.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>DSC_0501.jpg</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>'DSC_0501.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>DSC_0502.jpg</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>'DSC_0502.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>DSC_0503.jpg</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>'DSC_0503.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>DSC_0504.jpg</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>'DSC_0504.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>DSC_0505.jpg</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>'DSC_0505.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>DSC_0506.jpg</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>'DSC_0506.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>DSC_0508.jpg</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>'DSC_0508.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>DSC_0509.jpg</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>'DSC_0509.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>DSC_0510.jpg</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>'DSC_0510.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>DSC_0511.jpg</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>'DSC_0511.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>DSC_0512.jpg</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>'DSC_0512.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>DSC_0513.jpg</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>'DSC_0513.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>DSC_0514.jpg</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>'DSC_0514.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>DSC_0515.jpg</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>'DSC_0515.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>DSC_0516.jpg</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>'DSC_0516.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>DSC_0517.jpg</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>'DSC_0517.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>DSC_0518.jpg</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>'DSC_0518.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>DSC_0519.jpg</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>'DSC_0519.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>DSC_0520.jpg</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>'DSC_0520.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>DSC_0521.jpg</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>'DSC_0521.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>DSC_0522.jpg</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>'DSC_0522.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>DSC_0523.jpg</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>'DSC_0523.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>DSC_0524.jpg</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>'DSC_0524.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>DSC_0525.jpg</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>'DSC_0525.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>DSC_0526.jpg</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>'DSC_0526.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>DSC_0527.jpg</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>'DSC_0527.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>DSC_0528.jpg</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>'DSC_0528.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>DSC_0529.jpg</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>'DSC_0529.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>DSC_0530.jpg</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>'DSC_0530.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>DSC_0531.jpg</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>'DSC_0531.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>DSC_0532.jpg</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>'DSC_0532.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>DSC_0533.jpg</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>'DSC_0533.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>DSC_0534.jpg</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>'DSC_0534.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>DSC_0535.jpg</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>'DSC_0535.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>DSC_0536.jpg</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>'DSC_0536.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>DSC_0537.jpg</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>'DSC_0537.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>DSC_0538.jpg</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>'DSC_0538.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>DSC_0540.jpg</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>'DSC_0540.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>DSC_0541.jpg</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>'DSC_0541.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>DSC_0543.jpg</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>'DSC_0543.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>DSC_0544.jpg</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>'DSC_0544.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>DSC_0545.jpg</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>'DSC_0545.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>DSC_0546.jpg</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>'DSC_0546.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>DSC_0547.jpg</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>'DSC_0547.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>DSC_0548.jpg</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>'DSC_0548.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>DSC_0549.jpg</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>'DSC_0549.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>DSC_0550.jpg</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>'DSC_0550.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>DSC_0551.jpg</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>'DSC_0551.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>DSC_0552.jpg</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>'DSC_0552.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>DSC_0553.jpg</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>'DSC_0553.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>DSC_0554.jpg</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>'DSC_0554.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>DSC_0555.jpg</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>'DSC_0555.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>DSC_0556.jpg</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>'DSC_0556.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>DSC_0557.jpg</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>'DSC_0557.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>DSC_0558.jpg</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>'DSC_0558.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>DSC_0559.jpg</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>'DSC_0559.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>DSC_0560.jpg</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>'DSC_0560.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>DSC_0561.jpg</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>'DSC_0561.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>DSC_0562.jpg</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>'DSC_0562.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>DSC_0563.jpg</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>'DSC_0563.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>DSC_0564.jpg</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>'DSC_0564.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>DSC_0565.jpg</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>'DSC_0565.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>DSC_0567.jpg</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>'DSC_0567.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>DSC_0568.jpg</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>'DSC_0568.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>DSC_0569.jpg</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>'DSC_0569.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>DSC_0570.jpg</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>'DSC_0570.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>DSC_0571.jpg</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>'DSC_0571.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>DSC_0572.jpg</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>'DSC_0572.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>DSC_0575.jpg</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>'DSC_0575.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>DSC_0576.jpg</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>'DSC_0576.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>DSC_0577.jpg</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>'DSC_0577.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>DSC_0578.jpg</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>'DSC_0578.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>DSC_0579.jpg</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>'DSC_0579.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>DSC_0580.jpg</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>'DSC_0580.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>DSC_0581.jpg</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>'DSC_0581.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>DSC_0582.jpg</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>'DSC_0582.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>DSC_0583.jpg</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>'DSC_0583.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>DSC_0586.jpg</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>'DSC_0586.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>DSC_0587.jpg</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>'DSC_0587.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>DSC_0588.jpg</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>'DSC_0588.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>DSC_0590.jpg</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>'DSC_0590.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>DSC_0591.jpg</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>'DSC_0591.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>DSC_0592.jpg</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>'DSC_0592.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>DSC_0593.jpg</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>'DSC_0593.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>DSC_0594.jpg</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>'DSC_0594.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>DSC_0595.jpg</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>'DSC_0595.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>DSC_0596.jpg</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>'DSC_0596.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>DSC_0597.jpg</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>'DSC_0597.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>DSC_0598.jpg</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>'DSC_0598.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>DSC_0600.jpg</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>'DSC_0600.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>DSC_0601.jpg</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>'DSC_0601.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>DSC_0602.jpg</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>'DSC_0602.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>DSC_0604.jpg</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>'DSC_0604.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>DSC_0606.jpg</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>'DSC_0606.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>DSC_0607.jpg</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>'DSC_0607.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>DSC_0608.jpg</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>'DSC_0608.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>DSC_0609.jpg</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>'DSC_0609.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>DSC_0611.jpg</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>'DSC_0611.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>DSC_0612.jpg</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>'DSC_0612.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>DSC_0613.jpg</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>'DSC_0613.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>DSC_0614.jpg</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>'DSC_0614.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>DSC_0615.jpg</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>'DSC_0615.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>DSC_0616.jpg</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>'DSC_0616.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>DSC_0618.jpg</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>'DSC_0618.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>DSC_0619.jpg</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>'DSC_0619.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>DSC_0620.jpg</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>'DSC_0620.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>DSC_0621.jpg</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>'DSC_0621.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>DSC_0622.jpg</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>'DSC_0622.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>DSC_0623.jpg</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>'DSC_0623.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>DSC_0624.jpg</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>'DSC_0624.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>DSC_0625.jpg</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>'DSC_0625.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>DSC_0627.jpg</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>'DSC_0627.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>DSC_0628.jpg</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>'DSC_0628.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>DSC_0629.jpg</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>'DSC_0629.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>DSC_0632.jpg</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>'DSC_0632.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>DSC_0633.jpg</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>'DSC_0633.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>DSC_0635.jpg</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>'DSC_0635.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>DSC_0636.jpg</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>'DSC_0636.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>DSC_0637.jpg</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>'DSC_0637.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>DSC_0638.jpg</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>'DSC_0638.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>DSC_0639.jpg</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>'DSC_0639.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>DSC_0640.jpg</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>'DSC_0640.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>DSC_0641.jpg</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>'DSC_0641.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>DSC_0643.jpg</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>'DSC_0643.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>DSC_0644.jpg</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>'DSC_0644.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>DSC_0645.jpg</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>'DSC_0645.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>DSC_0646.jpg</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>'DSC_0646.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>DSC_0647.jpg</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>'DSC_0647.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>DSC_0648.jpg</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>'DSC_0648.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>DSC_0649.jpg</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>'DSC_0649.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>DSC_0650.jpg</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>'DSC_0650.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>DSC_0651.jpg</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>'DSC_0651.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>DSC_0652.jpg</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>'DSC_0652.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>DSC_0653.jpg</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>'DSC_0653.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>DSC_0654.jpg</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>'DSC_0654.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>DSC_0655.jpg</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>'DSC_0655.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>DSC_0656.jpg</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>'DSC_0656.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>DSC_0657.jpg</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>'DSC_0657.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>DSC_0658.jpg</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>'DSC_0658.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>DSC_0659.jpg</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>'DSC_0659.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>DSC_0661.jpg</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>'DSC_0661.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>DSC_0662.jpg</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>'DSC_0662.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>DSC_0663.jpg</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>'DSC_0663.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>DSC_0664.jpg</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>'DSC_0664.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>DSC_0665.jpg</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>'DSC_0665.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>DSC_0666.jpg</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>'DSC_0666.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>DSC_0668.jpg</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>'DSC_0668.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>DSC_0669.jpg</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>'DSC_0669.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>DSC_0670.jpg</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>'DSC_0670.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>DSC_0671.jpg</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>'DSC_0671.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>DSC_0672.jpg</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>'DSC_0672.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>DSC_0673.jpg</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>'DSC_0673.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>DSC_0674.jpg</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>'DSC_0674.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>DSC_0675.jpg</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>'DSC_0675.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>DSC_0676.jpg</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>'DSC_0676.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>DSC_0677.jpg</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>'DSC_0677.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>DSC_0678.jpg</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>'DSC_0678.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>DSC_0679.jpg</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>'DSC_0679.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>DSC_0680.jpg</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>'DSC_0680.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>DSC_0681.jpg</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>'DSC_0681.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>DSC_0682.jpg</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>'DSC_0682.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>DSC_0683.jpg</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>'DSC_0683.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>DSC_0684.jpg</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>'DSC_0684.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>DSC_0685.jpg</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>'DSC_0685.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>DSC_0686.jpg</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>'DSC_0686.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>DSC_0687.jpg</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>'DSC_0687.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>DSC_0688.jpg</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>'DSC_0688.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>DSC_0689.jpg</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>'DSC_0689.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>DSC_0690.jpg</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>'DSC_0690.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>DSC_0691.jpg</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>'DSC_0691.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>DSC_0692.jpg</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>'DSC_0692.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>DSC_0694.jpg</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>'DSC_0694.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>DSC_0696.jpg</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>'DSC_0696.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>DSC_0697.jpg</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>'DSC_0697.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>DSC_0699.jpg</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>'DSC_0699.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>DSC_0701.jpg</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>'DSC_0701.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>DSC_0703.jpg</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>'DSC_0703.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>DSC_0705.jpg</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>'DSC_0705.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>DSC_0706.jpg</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>'DSC_0706.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>DSC_0707.jpg</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>'DSC_0707.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>DSC_0708.jpg</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>'DSC_0708.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>DSC_0709.jpg</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>'DSC_0709.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>DSC_0710.jpg</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>'DSC_0710.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>DSC_0711.jpg</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>'DSC_0711.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>DSC_0712.jpg</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>'DSC_0712.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>DSC_0715.jpg</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>'DSC_0715.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>DSC_0716.jpg</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>'DSC_0716.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>DSC_0717.jpg</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>'DSC_0717.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>DSC_0720.jpg</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>'DSC_0720.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>DSC_0721.jpg</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>'DSC_0721.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>DSC_0722.jpg</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>'DSC_0722.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>DSC_0723.jpg</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>'DSC_0723.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>DSC_0724.jpg</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>'DSC_0724.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>DSC_0725.jpg</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>'DSC_0725.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>DSC_0726.jpg</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>'DSC_0726.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>DSC_0727.jpg</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>'DSC_0727.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>DSC_0731.jpg</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>'DSC_0731.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>DSC_0732.jpg</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>'DSC_0732.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>DSC_0733.jpg</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>'DSC_0733.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>DSC_0734.jpg</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>'DSC_0734.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>DSC_0735.jpg</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>'DSC_0735.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>DSC_0736.jpg</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>'DSC_0736.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>DSC_0737.jpg</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>'DSC_0737.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>DSC_0738.jpg</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>'DSC_0738.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>DSC_0739.jpg</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>'DSC_0739.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>DSC_0740.jpg</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>'DSC_0740.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>DSC_0741.jpg</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>'DSC_0741.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>DSC_0742.jpg</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>'DSC_0742.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>DSC_0744.jpg</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>'DSC_0744.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>DSC_0746.jpg</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>'DSC_0746.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>DSC_0747.jpg</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>'DSC_0747.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>DSC_0748.jpg</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>'DSC_0748.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>DSC_0749.jpg</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>'DSC_0749.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>DSC_0750.jpg</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>'DSC_0750.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>DSC_0752.jpg</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>'DSC_0752.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>DSC_0753.jpg</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>'DSC_0753.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>DSC_0754.jpg</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>'DSC_0754.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>DSC_0755.jpg</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>'DSC_0755.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>DSC_0757.jpg</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>'DSC_0757.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>DSC_0758.jpg</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>'DSC_0758.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>DSC_0759.jpg</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>'DSC_0759.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>DSC_0760.jpg</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>'DSC_0760.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>DSC_0762.jpg</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>'DSC_0762.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>DSC_0763.jpg</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>'DSC_0763.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>DSC_0765.jpg</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>'DSC_0765.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>DSC_0766.jpg</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>'DSC_0766.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>DSC_0769.jpg</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>'DSC_0769.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>DSC_0770.jpg</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>'DSC_0770.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>DSC_0771.jpg</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>'DSC_0771.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>DSC_0772.jpg</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>'DSC_0772.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>DSC_0773.jpg</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>'DSC_0773.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>DSC_0774.jpg</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>'DSC_0774.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>DSC_0775.jpg</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>'DSC_0775.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>DSC_0776.jpg</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>'DSC_0776.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>DSC_0777.jpg</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>'DSC_0777.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>DSC_0778.jpg</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>'DSC_0778.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>DSC_0779.jpg</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>'DSC_0779.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>DSC_0780.jpg</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>'DSC_0780.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>DSC_0781.jpg</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>'DSC_0781.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>DSC_0782.jpg</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>'DSC_0782.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>DSC_0783.jpg</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>'DSC_0783.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>DSC_0784.jpg</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>'DSC_0784.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>DSC_0785.jpg</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>'DSC_0785.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>DSC_0786.jpg</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>'DSC_0786.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>DSC_0787.jpg</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>'DSC_0787.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>DSC_0788.jpg</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>'DSC_0788.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>DSC_0789.jpg</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>'DSC_0789.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>DSC_0790.jpg</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>'DSC_0790.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>DSC_0791.jpg</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>'DSC_0791.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>DSC_0792.jpg</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>'DSC_0792.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>DSC_0793.jpg</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>'DSC_0793.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>DSC_0794.jpg</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>'DSC_0794.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>DSC_0795.jpg</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>'DSC_0795.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>DSC_0796.jpg</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>'DSC_0796.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>DSC_0797.jpg</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>'DSC_0797.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>DSC_0798.jpg</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>'DSC_0798.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>DSC_0799.jpg</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>'DSC_0799.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>DSC_0800.jpg</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>'DSC_0800.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>DSC_0801.jpg</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>'DSC_0801.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>DSC_0802.jpg</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>'DSC_0802.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>DSC_0803.jpg</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>'DSC_0803.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>DSC_0804.jpg</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>'DSC_0804.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>DSC_0805.jpg</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>'DSC_0805.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>DSC_0806.jpg</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>'DSC_0806.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>DSC_0807.jpg</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>'DSC_0807.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>DSC_0808.jpg</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>'DSC_0808.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>DSC_0809.jpg</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>'DSC_0809.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>DSC_0810.jpg</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>'DSC_0810.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>DSC_0811.jpg</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>'DSC_0811.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>DSC_0812.jpg</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>'DSC_0812.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>DSC_0813.jpg</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>'DSC_0813.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>DSC_0814.jpg</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>'DSC_0814.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>DSC_0815.jpg</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>'DSC_0815.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>DSC_0816.jpg</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>'DSC_0816.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>DSC_0817.jpg</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>'DSC_0817.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>DSC_0818.jpg</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>'DSC_0818.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>DSC_0819.jpg</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>'DSC_0819.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>DSC_0820.jpg</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>'DSC_0820.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>DSC_0821.jpg</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>'DSC_0821.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>DSC_0822.jpg</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>'DSC_0822.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>DSC_0823.jpg</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>'DSC_0823.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>DSC_0824.jpg</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>'DSC_0824.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>DSC_0825.jpg</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>'DSC_0825.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>DSC_0826.jpg</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>'DSC_0826.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>DSC_0827.jpg</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>'DSC_0827.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>DSC_0828.jpg</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>'DSC_0828.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>DSC_0829.jpg</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>'DSC_0829.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>DSC_0830.jpg</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>'DSC_0830.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>DSC_0831.jpg</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>'DSC_0831.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>DSC_0832.jpg</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>'DSC_0832.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>DSC_0833.jpg</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>'DSC_0833.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>DSC_0834.jpg</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>'DSC_0834.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>DSC_0835.jpg</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>'DSC_0835.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>DSC_0836.jpg</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>'DSC_0836.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>DSC_0837.jpg</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>'DSC_0837.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>DSC_0838.jpg</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>'DSC_0838.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>DSC_0839.jpg</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>'DSC_0839.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>DSC_0840.jpg</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>'DSC_0840.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>DSC_0841.jpg</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>'DSC_0841.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>DSC_0842.jpg</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>'DSC_0842.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>DSC_0843.jpg</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>'DSC_0843.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>DSC_0844.jpg</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>'DSC_0844.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>DSC_0845.jpg</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>'DSC_0845.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>DSC_0846.jpg</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>'DSC_0846.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>DSC_0847.jpg</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>'DSC_0847.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>DSC_0848.jpg</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>'DSC_0848.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>DSC_0849.jpg</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>'DSC_0849.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>DSC_0850.jpg</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>'DSC_0850.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>DSC_0852.jpg</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>'DSC_0852.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>DSC_0853.jpg</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>'DSC_0853.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>DSC_0854.jpg</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>'DSC_0854.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>DSC_0857.jpg</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>'DSC_0857.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>DSC_0858.jpg</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>'DSC_0858.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>DSC_0859.jpg</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>'DSC_0859.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>DSC_0860.jpg</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>'DSC_0860.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>DSC_0861.jpg</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>'DSC_0861.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>DSC_0862.jpg</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>'DSC_0862.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>DSC_0863.jpg</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>'DSC_0863.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>DSC_0864.jpg</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>'DSC_0864.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>DSC_0865.jpg</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>'DSC_0865.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>DSC_0866.jpg</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>'DSC_0866.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>DSC_0867.jpg</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>'DSC_0867.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>DSC_0868.jpg</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>'DSC_0868.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>DSC_0869.jpg</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>'DSC_0869.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>DSC_0870.jpg</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>'DSC_0870.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>DSC_0871.jpg</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>'DSC_0871.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>DSC_0872.jpg</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>'DSC_0872.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>DSC_0873.jpg</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>'DSC_0873.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>DSC_0874.jpg</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>'DSC_0874.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>DSC_0875.jpg</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>'DSC_0875.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>DSC_0876.jpg</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>'DSC_0876.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>DSC_0877.jpg</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>'DSC_0877.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>DSC_0879.jpg</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>'DSC_0879.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>DSC_0880.jpg</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>'DSC_0880.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>DSC_0881.jpg</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>'DSC_0881.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>DSC_0882.jpg</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>'DSC_0882.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>DSC_0883.jpg</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>'DSC_0883.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>DSC_0884.jpg</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>'DSC_0884.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>DSC_0885.jpg</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>'DSC_0885.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>DSC_0887.jpg</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>'DSC_0887.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>DSC_0888.jpg</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>'DSC_0888.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>DSC_0889.jpg</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>'DSC_0889.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>DSC_0890.jpg</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>'DSC_0890.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>DSC_0891.jpg</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>'DSC_0891.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>DSC_0892.jpg</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>'DSC_0892.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>DSC_0893.jpg</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>'DSC_0893.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>DSC_0894.jpg</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>'DSC_0894.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>DSC_0895.jpg</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>'DSC_0895.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>DSC_0897.jpg</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>'DSC_0897.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>DSC_0899.jpg</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>'DSC_0899.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>DSC_0900.jpg</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>'DSC_0900.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>DSC_0901.jpg</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>'DSC_0901.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>DSC_0902.jpg</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>'DSC_0902.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>DSC_0903.jpg</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>'DSC_0903.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>DSC_0904.jpg</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>'DSC_0904.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>DSC_0905.jpg</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>'DSC_0905.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>DSC_0906.jpg</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>'DSC_0906.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>DSC_0907.jpg</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>'DSC_0907.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>DSC_0908.jpg</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>'DSC_0908.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>DSC_0909.jpg</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>'DSC_0909.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>DSC_0910.jpg</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>'DSC_0910.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>DSC_0911.jpg</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>'DSC_0911.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>DSC_0912.jpg</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>'DSC_0912.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>DSC_0913.jpg</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>'DSC_0913.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>DSC_0914.jpg</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>'DSC_0914.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>DSC_0916.jpg</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>'DSC_0916.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>DSC_0917.jpg</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>'DSC_0917.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>DSC_0918.jpg</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>'DSC_0918.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>DSC_0919.jpg</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>'DSC_0919.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>DSC_0920.jpg</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>'DSC_0920.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>DSC_0921.jpg</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>'DSC_0921.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>DSC_0922.jpg</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>'DSC_0922.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>DSC_0924.jpg</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>'DSC_0924.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>DSC_0925.jpg</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>'DSC_0925.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>DSC_0926.jpg</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>'DSC_0926.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>DSC_0927.jpg</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>'DSC_0927.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>DSC_0928.jpg</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>'DSC_0928.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>DSC_0929.jpg</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>'DSC_0929.jpg',</t>
         </is>
       </c>
     </row>

--- a/archivos_listados.xlsx
+++ b/archivos_listados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B153"/>
+  <dimension ref="A1:B714"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,1824 +443,8556 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DSC_0465.jpg</t>
+          <t>DSC_0005.jpg</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>'DSC_0465.jpg',</t>
+          <t>'DSC_0005.jpg',</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DSC_0466.jpg</t>
+          <t>DSC_0006.jpg</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>'DSC_0466.jpg',</t>
+          <t>'DSC_0006.jpg',</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DSC_0467.jpg</t>
+          <t>DSC_0007.jpg</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>'DSC_0467.jpg',</t>
+          <t>'DSC_0007.jpg',</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DSC_0468.jpg</t>
+          <t>DSC_0008.jpg</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>'DSC_0468.jpg',</t>
+          <t>'DSC_0008.jpg',</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DSC_0469.jpg</t>
+          <t>DSC_0009.jpg</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>'DSC_0469.jpg',</t>
+          <t>'DSC_0009.jpg',</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DSC_0471.jpg</t>
+          <t>DSC_0010.jpg</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>'DSC_0471.jpg',</t>
+          <t>'DSC_0010.jpg',</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DSC_0472.jpg</t>
+          <t>DSC_0011.jpg</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>'DSC_0472.jpg',</t>
+          <t>'DSC_0011.jpg',</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DSC_0473.jpg</t>
+          <t>DSC_0012.jpg</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>'DSC_0473.jpg',</t>
+          <t>'DSC_0012.jpg',</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DSC_0474.jpg</t>
+          <t>DSC_0013.jpg</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>'DSC_0474.jpg',</t>
+          <t>'DSC_0013.jpg',</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DSC_0475.jpg</t>
+          <t>DSC_0014.jpg</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>'DSC_0475.jpg',</t>
+          <t>'DSC_0014.jpg',</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DSC_0476.jpg</t>
+          <t>DSC_0015.jpg</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>'DSC_0476.jpg',</t>
+          <t>'DSC_0015.jpg',</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DSC_0479.jpg</t>
+          <t>DSC_0016.jpg</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>'DSC_0479.jpg',</t>
+          <t>'DSC_0016.jpg',</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DSC_0482.jpg</t>
+          <t>DSC_0017.jpg</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>'DSC_0482.jpg',</t>
+          <t>'DSC_0017.jpg',</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DSC_0483.jpg</t>
+          <t>DSC_0018.jpg</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>'DSC_0483.jpg',</t>
+          <t>'DSC_0018.jpg',</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DSC_0486.jpg</t>
+          <t>DSC_0019.jpg</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>'DSC_0486.jpg',</t>
+          <t>'DSC_0019.jpg',</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DSC_0491.jpg</t>
+          <t>DSC_0020.jpg</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>'DSC_0491.jpg',</t>
+          <t>'DSC_0020.jpg',</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DSC_0492.jpg</t>
+          <t>DSC_0021.jpg</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>'DSC_0492.jpg',</t>
+          <t>'DSC_0021.jpg',</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DSC_0494.jpg</t>
+          <t>DSC_0022.jpg</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>'DSC_0494.jpg',</t>
+          <t>'DSC_0022.jpg',</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DSC_0495.jpg</t>
+          <t>DSC_0023.jpg</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>'DSC_0495.jpg',</t>
+          <t>'DSC_0023.jpg',</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DSC_0497.jpg</t>
+          <t>DSC_0024.jpg</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>'DSC_0497.jpg',</t>
+          <t>'DSC_0024.jpg',</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DSC_0498.jpg</t>
+          <t>DSC_0025.jpg</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>'DSC_0498.jpg',</t>
+          <t>'DSC_0025.jpg',</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DSC_0499.jpg</t>
+          <t>DSC_0026.jpg</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>'DSC_0499.jpg',</t>
+          <t>'DSC_0026.jpg',</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DSC_0500.jpg</t>
+          <t>DSC_0027.jpg</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>'DSC_0500.jpg',</t>
+          <t>'DSC_0027.jpg',</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DSC_0501.jpg</t>
+          <t>DSC_0028.jpg</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>'DSC_0501.jpg',</t>
+          <t>'DSC_0028.jpg',</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DSC_0502.jpg</t>
+          <t>DSC_0029.jpg</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>'DSC_0502.jpg',</t>
+          <t>'DSC_0029.jpg',</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DSC_0503.jpg</t>
+          <t>DSC_0030.jpg</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>'DSC_0503.jpg',</t>
+          <t>'DSC_0030.jpg',</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DSC_0505.jpg</t>
+          <t>DSC_0031.jpg</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>'DSC_0505.jpg',</t>
+          <t>'DSC_0031.jpg',</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DSC_0506.jpg</t>
+          <t>DSC_0032.jpg</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>'DSC_0506.jpg',</t>
+          <t>'DSC_0032.jpg',</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DSC_0507.jpg</t>
+          <t>DSC_0033.jpg</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>'DSC_0507.jpg',</t>
+          <t>'DSC_0033.jpg',</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DSC_0508.jpg</t>
+          <t>DSC_0034.jpg</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>'DSC_0508.jpg',</t>
+          <t>'DSC_0034.jpg',</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DSC_0509.jpg</t>
+          <t>DSC_0035.jpg</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>'DSC_0509.jpg',</t>
+          <t>'DSC_0035.jpg',</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DSC_0510.jpg</t>
+          <t>DSC_0036.jpg</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>'DSC_0510.jpg',</t>
+          <t>'DSC_0036.jpg',</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DSC_0511.jpg</t>
+          <t>DSC_0037.jpg</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>'DSC_0511.jpg',</t>
+          <t>'DSC_0037.jpg',</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DSC_0512.jpg</t>
+          <t>DSC_0038.jpg</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>'DSC_0512.jpg',</t>
+          <t>'DSC_0038.jpg',</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DSC_0513.jpg</t>
+          <t>DSC_0039.jpg</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>'DSC_0513.jpg',</t>
+          <t>'DSC_0039.jpg',</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DSC_0514.jpg</t>
+          <t>DSC_0040.jpg</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>'DSC_0514.jpg',</t>
+          <t>'DSC_0040.jpg',</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DSC_0515.jpg</t>
+          <t>DSC_0042.jpg</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>'DSC_0515.jpg',</t>
+          <t>'DSC_0042.jpg',</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DSC_0518.jpg</t>
+          <t>DSC_0043.jpg</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>'DSC_0518.jpg',</t>
+          <t>'DSC_0043.jpg',</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DSC_0519.jpg</t>
+          <t>DSC_0044.jpg</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>'DSC_0519.jpg',</t>
+          <t>'DSC_0044.jpg',</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DSC_0520.jpg</t>
+          <t>DSC_0045.jpg</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>'DSC_0520.jpg',</t>
+          <t>'DSC_0045.jpg',</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DSC_0521.jpg</t>
+          <t>DSC_0046.jpg</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>'DSC_0521.jpg',</t>
+          <t>'DSC_0046.jpg',</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DSC_0522.jpg</t>
+          <t>DSC_0048.jpg</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>'DSC_0522.jpg',</t>
+          <t>'DSC_0048.jpg',</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DSC_0523.jpg</t>
+          <t>DSC_0050.jpg</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>'DSC_0523.jpg',</t>
+          <t>'DSC_0050.jpg',</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DSC_0524.jpg</t>
+          <t>DSC_0051.jpg</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>'DSC_0524.jpg',</t>
+          <t>'DSC_0051.jpg',</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DSC_0525.jpg</t>
+          <t>DSC_0053.jpg</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>'DSC_0525.jpg',</t>
+          <t>'DSC_0053.jpg',</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DSC_0526.jpg</t>
+          <t>DSC_0056.jpg</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>'DSC_0526.jpg',</t>
+          <t>'DSC_0056.jpg',</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DSC_0527.jpg</t>
+          <t>DSC_0057.jpg</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>'DSC_0527.jpg',</t>
+          <t>'DSC_0057.jpg',</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DSC_0529.jpg</t>
+          <t>DSC_0058.jpg</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>'DSC_0529.jpg',</t>
+          <t>'DSC_0058.jpg',</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DSC_0531.jpg</t>
+          <t>DSC_0059.jpg</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>'DSC_0531.jpg',</t>
+          <t>'DSC_0059.jpg',</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DSC_0532.jpg</t>
+          <t>DSC_0060.jpg</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>'DSC_0532.jpg',</t>
+          <t>'DSC_0060.jpg',</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DSC_0533.jpg</t>
+          <t>DSC_0061.jpg</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>'DSC_0533.jpg',</t>
+          <t>'DSC_0061.jpg',</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DSC_0534.jpg</t>
+          <t>DSC_0062.jpg</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>'DSC_0534.jpg',</t>
+          <t>'DSC_0062.jpg',</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DSC_0535.jpg</t>
+          <t>DSC_0063.jpg</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>'DSC_0535.jpg',</t>
+          <t>'DSC_0063.jpg',</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DSC_0536.jpg</t>
+          <t>DSC_0064.jpg</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>'DSC_0536.jpg',</t>
+          <t>'DSC_0064.jpg',</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DSC_0538.jpg</t>
+          <t>DSC_0065.jpg</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>'DSC_0538.jpg',</t>
+          <t>'DSC_0065.jpg',</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DSC_0539.jpg</t>
+          <t>DSC_0066.jpg</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>'DSC_0539.jpg',</t>
+          <t>'DSC_0066.jpg',</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DSC_0542.jpg</t>
+          <t>DSC_0067.jpg</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>'DSC_0542.jpg',</t>
+          <t>'DSC_0067.jpg',</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DSC_0543.jpg</t>
+          <t>DSC_0068.jpg</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>'DSC_0543.jpg',</t>
+          <t>'DSC_0068.jpg',</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DSC_0545.jpg</t>
+          <t>DSC_0069.jpg</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>'DSC_0545.jpg',</t>
+          <t>'DSC_0069.jpg',</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DSC_0548.jpg</t>
+          <t>DSC_0071.jpg</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>'DSC_0548.jpg',</t>
+          <t>'DSC_0071.jpg',</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DSC_0551.jpg</t>
+          <t>DSC_0072.jpg</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>'DSC_0551.jpg',</t>
+          <t>'DSC_0072.jpg',</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DSC_0552.jpg</t>
+          <t>DSC_0073.jpg</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>'DSC_0552.jpg',</t>
+          <t>'DSC_0073.jpg',</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DSC_0555.jpg</t>
+          <t>DSC_0074.jpg</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>'DSC_0555.jpg',</t>
+          <t>'DSC_0074.jpg',</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DSC_0557.jpg</t>
+          <t>DSC_0075.jpg</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>'DSC_0557.jpg',</t>
+          <t>'DSC_0075.jpg',</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>DSC_0558.jpg</t>
+          <t>DSC_0076.jpg</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>'DSC_0558.jpg',</t>
+          <t>'DSC_0076.jpg',</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>DSC_0559.jpg</t>
+          <t>DSC_0077.jpg</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>'DSC_0559.jpg',</t>
+          <t>'DSC_0077.jpg',</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>DSC_0561.jpg</t>
+          <t>DSC_0078.jpg</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>'DSC_0561.jpg',</t>
+          <t>'DSC_0078.jpg',</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>DSC_0562.jpg</t>
+          <t>DSC_0080.jpg</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>'DSC_0562.jpg',</t>
+          <t>'DSC_0080.jpg',</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>DSC_0563.jpg</t>
+          <t>DSC_0081.jpg</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>'DSC_0563.jpg',</t>
+          <t>'DSC_0081.jpg',</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>DSC_0565.jpg</t>
+          <t>DSC_0082.jpg</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>'DSC_0565.jpg',</t>
+          <t>'DSC_0082.jpg',</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>DSC_0566.jpg</t>
+          <t>DSC_0083.jpg</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>'DSC_0566.jpg',</t>
+          <t>'DSC_0083.jpg',</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DSC_0567.jpg</t>
+          <t>DSC_0084.jpg</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>'DSC_0567.jpg',</t>
+          <t>'DSC_0084.jpg',</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>DSC_0568.jpg</t>
+          <t>DSC_0085.jpg</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>'DSC_0568.jpg',</t>
+          <t>'DSC_0085.jpg',</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DSC_0569.jpg</t>
+          <t>DSC_0086.jpg</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>'DSC_0569.jpg',</t>
+          <t>'DSC_0086.jpg',</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DSC_0570.jpg</t>
+          <t>DSC_0087.jpg</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>'DSC_0570.jpg',</t>
+          <t>'DSC_0087.jpg',</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DSC_0572.jpg</t>
+          <t>DSC_0088.jpg</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>'DSC_0572.jpg',</t>
+          <t>'DSC_0088.jpg',</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DSC_0573.jpg</t>
+          <t>DSC_0089.jpg</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>'DSC_0573.jpg',</t>
+          <t>'DSC_0089.jpg',</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>DSC_0574.jpg</t>
+          <t>DSC_0090.jpg</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>'DSC_0574.jpg',</t>
+          <t>'DSC_0090.jpg',</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>DSC_0575.jpg</t>
+          <t>DSC_0091.jpg</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>'DSC_0575.jpg',</t>
+          <t>'DSC_0091.jpg',</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>DSC_0576.jpg</t>
+          <t>DSC_0092.jpg</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>'DSC_0576.jpg',</t>
+          <t>'DSC_0092.jpg',</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>DSC_0578.jpg</t>
+          <t>DSC_0093.jpg</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>'DSC_0578.jpg',</t>
+          <t>'DSC_0093.jpg',</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>DSC_0580.jpg</t>
+          <t>DSC_0094.jpg</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>'DSC_0580.jpg',</t>
+          <t>'DSC_0094.jpg',</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>DSC_0582.jpg</t>
+          <t>DSC_0095.jpg</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>'DSC_0582.jpg',</t>
+          <t>'DSC_0095.jpg',</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>DSC_0583.jpg</t>
+          <t>DSC_0096.jpg</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>'DSC_0583.jpg',</t>
+          <t>'DSC_0096.jpg',</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DSC_0584.jpg</t>
+          <t>DSC_0098.jpg</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>'DSC_0584.jpg',</t>
+          <t>'DSC_0098.jpg',</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DSC_0591.jpg</t>
+          <t>DSC_0099.jpg</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>'DSC_0591.jpg',</t>
+          <t>'DSC_0099.jpg',</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DSC_0592.jpg</t>
+          <t>DSC_0100.jpg</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>'DSC_0592.jpg',</t>
+          <t>'DSC_0100.jpg',</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>DSC_0593.jpg</t>
+          <t>DSC_0101.jpg</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>'DSC_0593.jpg',</t>
+          <t>'DSC_0101.jpg',</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>DSC_0595.jpg</t>
+          <t>DSC_0102.jpg</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>'DSC_0595.jpg',</t>
+          <t>'DSC_0102.jpg',</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>DSC_0601.jpg</t>
+          <t>DSC_0103.jpg</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>'DSC_0601.jpg',</t>
+          <t>'DSC_0103.jpg',</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>DSC_0602.jpg</t>
+          <t>DSC_0104.jpg</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>'DSC_0602.jpg',</t>
+          <t>'DSC_0104.jpg',</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>DSC_0603.jpg</t>
+          <t>DSC_0105.jpg</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>'DSC_0603.jpg',</t>
+          <t>'DSC_0105.jpg',</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>DSC_0605.jpg</t>
+          <t>DSC_0106.jpg</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>'DSC_0605.jpg',</t>
+          <t>'DSC_0106.jpg',</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>DSC_0606.jpg</t>
+          <t>DSC_0107.jpg</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>'DSC_0606.jpg',</t>
+          <t>'DSC_0107.jpg',</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>DSC_0608.jpg</t>
+          <t>DSC_0108.jpg</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>'DSC_0608.jpg',</t>
+          <t>'DSC_0108.jpg',</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>DSC_0611.jpg</t>
+          <t>DSC_0109.jpg</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>'DSC_0611.jpg',</t>
+          <t>'DSC_0109.jpg',</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>DSC_0614.jpg</t>
+          <t>DSC_0110.jpg</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>'DSC_0614.jpg',</t>
+          <t>'DSC_0110.jpg',</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>DSC_0615.jpg</t>
+          <t>DSC_0111.jpg</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>'DSC_0615.jpg',</t>
+          <t>'DSC_0111.jpg',</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>DSC_0618.jpg</t>
+          <t>DSC_0112.jpg</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>'DSC_0618.jpg',</t>
+          <t>'DSC_0112.jpg',</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>DSC_0619.jpg</t>
+          <t>DSC_0113.jpg</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>'DSC_0619.jpg',</t>
+          <t>'DSC_0113.jpg',</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>DSC_0620.jpg</t>
+          <t>DSC_0114.jpg</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>'DSC_0620.jpg',</t>
+          <t>'DSC_0114.jpg',</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>DSC_0621.jpg</t>
+          <t>DSC_0115.jpg</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>'DSC_0621.jpg',</t>
+          <t>'DSC_0115.jpg',</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>DSC_0622.jpg</t>
+          <t>DSC_0116.jpg</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>'DSC_0622.jpg',</t>
+          <t>'DSC_0116.jpg',</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>DSC_0623.jpg</t>
+          <t>DSC_0117.jpg</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>'DSC_0623.jpg',</t>
+          <t>'DSC_0117.jpg',</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>DSC_0626.jpg</t>
+          <t>DSC_0118.jpg</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>'DSC_0626.jpg',</t>
+          <t>'DSC_0118.jpg',</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>DSC_0628.jpg</t>
+          <t>DSC_0119.jpg</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>'DSC_0628.jpg',</t>
+          <t>'DSC_0119.jpg',</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>DSC_0629.jpg</t>
+          <t>DSC_0120.jpg</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>'DSC_0629.jpg',</t>
+          <t>'DSC_0120.jpg',</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>DSC_0631.jpg</t>
+          <t>DSC_0125.jpg</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>'DSC_0631.jpg',</t>
+          <t>'DSC_0125.jpg',</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>DSC_0632.jpg</t>
+          <t>DSC_0126.jpg</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>'DSC_0632.jpg',</t>
+          <t>'DSC_0126.jpg',</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>DSC_0633.jpg</t>
+          <t>DSC_0127.jpg</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>'DSC_0633.jpg',</t>
+          <t>'DSC_0127.jpg',</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>DSC_0638.jpg</t>
+          <t>DSC_0128.jpg</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>'DSC_0638.jpg',</t>
+          <t>'DSC_0128.jpg',</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>DSC_0639.jpg</t>
+          <t>DSC_0129.jpg</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>'DSC_0639.jpg',</t>
+          <t>'DSC_0129.jpg',</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>DSC_0640.jpg</t>
+          <t>DSC_0130.jpg</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>'DSC_0640.jpg',</t>
+          <t>'DSC_0130.jpg',</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>DSC_0641.jpg</t>
+          <t>DSC_0133.jpg</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>'DSC_0641.jpg',</t>
+          <t>'DSC_0133.jpg',</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>DSC_0642.jpg</t>
+          <t>DSC_0134.jpg</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>'DSC_0642.jpg',</t>
+          <t>'DSC_0134.jpg',</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>DSC_0646.jpg</t>
+          <t>DSC_0135.jpg</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>'DSC_0646.jpg',</t>
+          <t>'DSC_0135.jpg',</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>DSC_0647.jpg</t>
+          <t>DSC_0136.jpg</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>'DSC_0647.jpg',</t>
+          <t>'DSC_0136.jpg',</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>DSC_0648.jpg</t>
+          <t>DSC_0137.jpg</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>'DSC_0648.jpg',</t>
+          <t>'DSC_0137.jpg',</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>DSC_0649.jpg</t>
+          <t>DSC_0138.jpg</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>'DSC_0649.jpg',</t>
+          <t>'DSC_0138.jpg',</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>DSC_0650.jpg</t>
+          <t>DSC_0139.jpg</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>'DSC_0650.jpg',</t>
+          <t>'DSC_0139.jpg',</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>DSC_0652.jpg</t>
+          <t>DSC_0140.jpg</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>'DSC_0652.jpg',</t>
+          <t>'DSC_0140.jpg',</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>DSC_0653.jpg</t>
+          <t>DSC_0141.jpg</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>'DSC_0653.jpg',</t>
+          <t>'DSC_0141.jpg',</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>DSC_0654.jpg</t>
+          <t>DSC_0142.jpg</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>'DSC_0654.jpg',</t>
+          <t>'DSC_0142.jpg',</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>DSC_0655.jpg</t>
+          <t>DSC_0143.jpg</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>'DSC_0655.jpg',</t>
+          <t>'DSC_0143.jpg',</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>DSC_0656.jpg</t>
+          <t>DSC_0145.jpg</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>'DSC_0656.jpg',</t>
+          <t>'DSC_0145.jpg',</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>DSC_0657.jpg</t>
+          <t>DSC_0146.jpg</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>'DSC_0657.jpg',</t>
+          <t>'DSC_0146.jpg',</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>DSC_0658.jpg</t>
+          <t>DSC_0147.jpg</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>'DSC_0658.jpg',</t>
+          <t>'DSC_0147.jpg',</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>DSC_0662.jpg</t>
+          <t>DSC_0148.jpg</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>'DSC_0662.jpg',</t>
+          <t>'DSC_0148.jpg',</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>DSC_0664.jpg</t>
+          <t>DSC_0149.jpg</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>'DSC_0664.jpg',</t>
+          <t>'DSC_0149.jpg',</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>DSC_0665.jpg</t>
+          <t>DSC_0150.jpg</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>'DSC_0665.jpg',</t>
+          <t>'DSC_0150.jpg',</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>DSC_0666.jpg</t>
+          <t>DSC_0151.jpg</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>'DSC_0666.jpg',</t>
+          <t>'DSC_0151.jpg',</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>DSC_0667.jpg</t>
+          <t>DSC_0153.jpg</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>'DSC_0667.jpg',</t>
+          <t>'DSC_0153.jpg',</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>DSC_0668.jpg</t>
+          <t>DSC_0154.jpg</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>'DSC_0668.jpg',</t>
+          <t>'DSC_0154.jpg',</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>DSC_0671.jpg</t>
+          <t>DSC_0155.jpg</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>'DSC_0671.jpg',</t>
+          <t>'DSC_0155.jpg',</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>DSC_0672.jpg</t>
+          <t>DSC_0157.jpg</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>'DSC_0672.jpg',</t>
+          <t>'DSC_0157.jpg',</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>DSC_0673.jpg</t>
+          <t>DSC_0158.jpg</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>'DSC_0673.jpg',</t>
+          <t>'DSC_0158.jpg',</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>DSC_0677.jpg</t>
+          <t>DSC_0159.jpg</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>'DSC_0677.jpg',</t>
+          <t>'DSC_0159.jpg',</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>DSC_0679.jpg</t>
+          <t>DSC_0160.jpg</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>'DSC_0679.jpg',</t>
+          <t>'DSC_0160.jpg',</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>DSC_0680.jpg</t>
+          <t>DSC_0162.jpg</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>'DSC_0680.jpg',</t>
+          <t>'DSC_0162.jpg',</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>DSC_0681.jpg</t>
+          <t>DSC_0163.jpg</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>'DSC_0681.jpg',</t>
+          <t>'DSC_0163.jpg',</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>DSC_0682.jpg</t>
+          <t>DSC_0164.jpg</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>'DSC_0682.jpg',</t>
+          <t>'DSC_0164.jpg',</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>DSC_0683.jpg</t>
+          <t>DSC_0165.jpg</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>'DSC_0683.jpg',</t>
+          <t>'DSC_0165.jpg',</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>DSC_0684.jpg</t>
+          <t>DSC_0166.jpg</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>'DSC_0684.jpg',</t>
+          <t>'DSC_0166.jpg',</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>DSC_0685.jpg</t>
+          <t>DSC_0167.jpg</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>'DSC_0685.jpg',</t>
+          <t>'DSC_0167.jpg',</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>DSC_0686.jpg</t>
+          <t>DSC_0168.jpg</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>'DSC_0686.jpg',</t>
+          <t>'DSC_0168.jpg',</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>DSC_0688.jpg</t>
+          <t>DSC_0169.jpg</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>'DSC_0688.jpg',</t>
+          <t>'DSC_0169.jpg',</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>DSC_0691.jpg</t>
+          <t>DSC_0170.jpg</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>'DSC_0691.jpg',</t>
+          <t>'DSC_0170.jpg',</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>DSC_0692.jpg</t>
+          <t>DSC_0171.jpg</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>'DSC_0692.jpg',</t>
+          <t>'DSC_0171.jpg',</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>DSC_0693.jpg</t>
+          <t>DSC_0172.jpg</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>'DSC_0693.jpg',</t>
+          <t>'DSC_0172.jpg',</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>DSC_0694.jpg</t>
+          <t>DSC_0173.jpg</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>'DSC_0694.jpg',</t>
+          <t>'DSC_0173.jpg',</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>DSC_0695.jpg</t>
+          <t>DSC_0174.jpg</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>'DSC_0695.jpg',</t>
+          <t>'DSC_0174.jpg',</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
+          <t>DSC_0175.jpg</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>'DSC_0175.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>DSC_0176.jpg</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>'DSC_0176.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>DSC_0177.jpg</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>'DSC_0177.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>DSC_0178.jpg</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>'DSC_0178.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>DSC_0179.jpg</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>'DSC_0179.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>DSC_0180.jpg</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>'DSC_0180.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>DSC_0181.jpg</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>'DSC_0181.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>DSC_0182.jpg</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>'DSC_0182.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>DSC_0183.jpg</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>'DSC_0183.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>DSC_0184.jpg</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>'DSC_0184.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>DSC_0185.jpg</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>'DSC_0185.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>DSC_0186.jpg</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>'DSC_0186.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>DSC_0187.jpg</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>'DSC_0187.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>DSC_0188.jpg</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>'DSC_0188.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>DSC_0189.jpg</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>'DSC_0189.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>DSC_0192.jpg</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>'DSC_0192.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>DSC_0193.jpg</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>'DSC_0193.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>DSC_0194.jpg</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>'DSC_0194.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>DSC_0195.jpg</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>'DSC_0195.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>DSC_0196.jpg</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>'DSC_0196.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>DSC_0197.jpg</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>'DSC_0197.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>DSC_0198.jpg</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>'DSC_0198.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>DSC_0199.jpg</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>'DSC_0199.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>DSC_0200.jpg</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>'DSC_0200.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>DSC_0201.jpg</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>'DSC_0201.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>DSC_0203.jpg</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>'DSC_0203.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>DSC_0204.jpg</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>'DSC_0204.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>DSC_0205.jpg</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>'DSC_0205.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>DSC_0206.jpg</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>'DSC_0206.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>DSC_0207.jpg</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>'DSC_0207.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>DSC_0208.jpg</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>'DSC_0208.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>DSC_0209.jpg</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>'DSC_0209.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>DSC_0210.jpg</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>'DSC_0210.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>DSC_0211.jpg</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>'DSC_0211.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>DSC_0213.jpg</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>'DSC_0213.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>DSC_0214.jpg</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>'DSC_0214.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>DSC_0215.jpg</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>'DSC_0215.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>DSC_0216.jpg</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>'DSC_0216.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>DSC_0217.jpg</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>'DSC_0217.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>DSC_0218.jpg</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>'DSC_0218.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>DSC_0219.jpg</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>'DSC_0219.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>DSC_0220.jpg</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>'DSC_0220.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>DSC_0221.jpg</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>'DSC_0221.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>DSC_0222.jpg</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>'DSC_0222.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>DSC_0224.jpg</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>'DSC_0224.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>DSC_0225.jpg</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>'DSC_0225.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>DSC_0226.jpg</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>'DSC_0226.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>DSC_0227.jpg</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>'DSC_0227.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>DSC_0228.jpg</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>'DSC_0228.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>DSC_0229.jpg</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>'DSC_0229.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>DSC_0230.jpg</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>'DSC_0230.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>DSC_0231.jpg</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>'DSC_0231.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>DSC_0232.jpg</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>'DSC_0232.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>DSC_0233.jpg</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>'DSC_0233.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>DSC_0234.jpg</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>'DSC_0234.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>DSC_0236.jpg</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>'DSC_0236.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>DSC_0237.jpg</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>'DSC_0237.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>DSC_0238.jpg</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>'DSC_0238.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>DSC_0239.jpg</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>'DSC_0239.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>DSC_0240.jpg</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>'DSC_0240.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>DSC_0241.jpg</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>'DSC_0241.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>DSC_0242.jpg</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>'DSC_0242.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>DSC_0243.jpg</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>'DSC_0243.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>DSC_0244.jpg</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>'DSC_0244.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>DSC_0245.jpg</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>'DSC_0245.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>DSC_0246.jpg</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>'DSC_0246.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>DSC_0247.jpg</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>'DSC_0247.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>DSC_0248.jpg</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>'DSC_0248.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>DSC_0249.jpg</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>'DSC_0249.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>DSC_0250.jpg</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>'DSC_0250.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>DSC_0251.jpg</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>'DSC_0251.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>DSC_0252.jpg</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>'DSC_0252.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>DSC_0253.jpg</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>'DSC_0253.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>DSC_0254.jpg</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>'DSC_0254.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>DSC_0255.jpg</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>'DSC_0255.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>DSC_0256.jpg</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>'DSC_0256.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>DSC_0257.jpg</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>'DSC_0257.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>DSC_0258.jpg</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>'DSC_0258.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>DSC_0259.jpg</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>'DSC_0259.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>DSC_0260.jpg</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>'DSC_0260.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>DSC_0261.jpg</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>'DSC_0261.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>DSC_0262.jpg</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>'DSC_0262.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>DSC_0263.jpg</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>'DSC_0263.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>DSC_0264.jpg</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>'DSC_0264.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>DSC_0265.jpg</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>'DSC_0265.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>DSC_0266.jpg</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>'DSC_0266.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>DSC_0267.jpg</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>'DSC_0267.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>DSC_0268.jpg</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>'DSC_0268.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>DSC_0269.jpg</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>'DSC_0269.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>DSC_0270.jpg</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>'DSC_0270.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>DSC_0272.jpg</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>'DSC_0272.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>DSC_0273.jpg</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>'DSC_0273.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>DSC_0274.jpg</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>'DSC_0274.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>DSC_0275.jpg</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>'DSC_0275.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>DSC_0276.jpg</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>'DSC_0276.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>DSC_0277.jpg</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>'DSC_0277.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>DSC_0278.jpg</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>'DSC_0278.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>DSC_0281.jpg</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>'DSC_0281.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>DSC_0282.jpg</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>'DSC_0282.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>DSC_0283.jpg</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>'DSC_0283.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>DSC_0285.jpg</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>'DSC_0285.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>DSC_0286.jpg</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>'DSC_0286.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>DSC_0287.jpg</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>'DSC_0287.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>DSC_0288.jpg</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>'DSC_0288.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>DSC_0289.jpg</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>'DSC_0289.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>DSC_0290.jpg</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>'DSC_0290.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>DSC_0291.jpg</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>'DSC_0291.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>DSC_0292.jpg</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>'DSC_0292.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>DSC_0293.jpg</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>'DSC_0293.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>DSC_0294.jpg</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>'DSC_0294.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>DSC_0295.jpg</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>'DSC_0295.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>DSC_0296.jpg</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>'DSC_0296.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>DSC_0297.jpg</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>'DSC_0297.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>DSC_0299.jpg</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>'DSC_0299.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>DSC_0300.jpg</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>'DSC_0300.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>DSC_0301.jpg</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>'DSC_0301.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>DSC_0302.jpg</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>'DSC_0302.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>DSC_0311.jpg</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>'DSC_0311.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>DSC_0312.jpg</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>'DSC_0312.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>DSC_0313.jpg</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>'DSC_0313.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>DSC_0315.jpg</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>'DSC_0315.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>DSC_0316.jpg</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>'DSC_0316.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>DSC_0317.jpg</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>'DSC_0317.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>DSC_0318.jpg</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>'DSC_0318.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>DSC_0319.jpg</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>'DSC_0319.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>DSC_0320.jpg</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>'DSC_0320.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>DSC_0321.jpg</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>'DSC_0321.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>DSC_0323.jpg</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>'DSC_0323.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>DSC_0324.jpg</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>'DSC_0324.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>DSC_0325.jpg</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>'DSC_0325.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>DSC_0326.jpg</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>'DSC_0326.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>DSC_0327.jpg</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>'DSC_0327.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>DSC_0328.jpg</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>'DSC_0328.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>DSC_0330.jpg</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>'DSC_0330.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>DSC_0331.jpg</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>'DSC_0331.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>DSC_0332.jpg</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>'DSC_0332.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>DSC_0333.jpg</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>'DSC_0333.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>DSC_0334.jpg</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>'DSC_0334.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>DSC_0335.jpg</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>'DSC_0335.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>DSC_0336.jpg</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>'DSC_0336.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>DSC_0337.jpg</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>'DSC_0337.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>DSC_0338.jpg</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>'DSC_0338.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>DSC_0339.jpg</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>'DSC_0339.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>DSC_0340.jpg</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>'DSC_0340.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>DSC_0341.jpg</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>'DSC_0341.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>DSC_0342.jpg</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>'DSC_0342.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>DSC_0343.jpg</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>'DSC_0343.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>DSC_0344.jpg</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>'DSC_0344.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>DSC_0345.jpg</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>'DSC_0345.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>DSC_0346.jpg</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>'DSC_0346.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>DSC_0347.jpg</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>'DSC_0347.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>DSC_0348.jpg</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>'DSC_0348.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>DSC_0349.jpg</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>'DSC_0349.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>DSC_0350.jpg</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>'DSC_0350.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>DSC_0351.jpg</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>'DSC_0351.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>DSC_0352.jpg</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>'DSC_0352.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>DSC_0353.jpg</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>'DSC_0353.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>DSC_0354.jpg</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>'DSC_0354.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>DSC_0355.jpg</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>'DSC_0355.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>DSC_0356.jpg</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>'DSC_0356.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>DSC_0357.jpg</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>'DSC_0357.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>DSC_0358.jpg</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>'DSC_0358.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>DSC_0360.jpg</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>'DSC_0360.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>DSC_0362.jpg</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>'DSC_0362.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>DSC_0364.jpg</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>'DSC_0364.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>DSC_0365.jpg</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>'DSC_0365.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>DSC_0366.jpg</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>'DSC_0366.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>DSC_0367.jpg</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>'DSC_0367.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>DSC_0368.jpg</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>'DSC_0368.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>DSC_0369.jpg</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>'DSC_0369.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>DSC_0370.jpg</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>'DSC_0370.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>DSC_0371.jpg</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>'DSC_0371.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>DSC_0372.jpg</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>'DSC_0372.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>DSC_0373.jpg</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>'DSC_0373.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>DSC_0375.jpg</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>'DSC_0375.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>DSC_0376.jpg</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>'DSC_0376.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>DSC_0377.jpg</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>'DSC_0377.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>DSC_0378.jpg</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>'DSC_0378.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>DSC_0379.jpg</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>'DSC_0379.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>DSC_0380.jpg</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>'DSC_0380.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>DSC_0381.jpg</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>'DSC_0381.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>DSC_0382.jpg</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>'DSC_0382.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>DSC_0385.jpg</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>'DSC_0385.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>DSC_0386.jpg</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>'DSC_0386.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>DSC_0387.jpg</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>'DSC_0387.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>DSC_0388.jpg</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>'DSC_0388.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>DSC_0393.jpg</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>'DSC_0393.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>DSC_0400.jpg</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>'DSC_0400.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>DSC_0401.jpg</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>'DSC_0401.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>DSC_0406.jpg</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>'DSC_0406.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>DSC_0407.jpg</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>'DSC_0407.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>DSC_0408.jpg</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>'DSC_0408.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>DSC_0409.jpg</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>'DSC_0409.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>DSC_0410.jpg</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>'DSC_0410.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>DSC_0411.jpg</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>'DSC_0411.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>DSC_0412.jpg</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>'DSC_0412.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>DSC_0413.jpg</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>'DSC_0413.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>DSC_0414.jpg</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>'DSC_0414.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>DSC_0415.jpg</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>'DSC_0415.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>DSC_0416.jpg</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>'DSC_0416.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>DSC_0417.jpg</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>'DSC_0417.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>DSC_0418.jpg</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>'DSC_0418.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>DSC_0423.jpg</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>'DSC_0423.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>DSC_0424.jpg</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>'DSC_0424.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>DSC_0425.jpg</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>'DSC_0425.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>DSC_0426.jpg</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>'DSC_0426.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>DSC_0427.jpg</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>'DSC_0427.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>DSC_0428.jpg</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>'DSC_0428.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>DSC_0429.jpg</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>'DSC_0429.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>DSC_0431.jpg</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>'DSC_0431.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>DSC_0432.jpg</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>'DSC_0432.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>DSC_0433.jpg</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>'DSC_0433.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>DSC_0434.jpg</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>'DSC_0434.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>DSC_0435.jpg</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>'DSC_0435.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>DSC_0439.jpg</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>'DSC_0439.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>DSC_0440.jpg</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>'DSC_0440.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>DSC_0441.jpg</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>'DSC_0441.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>DSC_0442.jpg</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>'DSC_0442.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>DSC_0443.jpg</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>'DSC_0443.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>DSC_0444.jpg</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>'DSC_0444.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>DSC_0445.jpg</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>'DSC_0445.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>DSC_0446.jpg</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>'DSC_0446.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>DSC_0447.jpg</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>'DSC_0447.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>DSC_0448.jpg</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>'DSC_0448.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>DSC_0449.jpg</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>'DSC_0449.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>DSC_0450.jpg</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>'DSC_0450.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>DSC_0451.jpg</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>'DSC_0451.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>DSC_0453.jpg</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>'DSC_0453.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>DSC_0454.jpg</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>'DSC_0454.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>DSC_0455.jpg</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>'DSC_0455.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>DSC_0456.jpg</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>'DSC_0456.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>DSC_0457.jpg</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>'DSC_0457.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>DSC_0458.jpg</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>'DSC_0458.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>DSC_0459.jpg</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>'DSC_0459.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>DSC_0460.jpg</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>'DSC_0460.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>DSC_0461.jpg</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>'DSC_0461.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>DSC_0462.jpg</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>'DSC_0462.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>DSC_0463.jpg</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>'DSC_0463.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>DSC_0464.jpg</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>'DSC_0464.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>DSC_0466.jpg</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>'DSC_0466.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>DSC_0467.jpg</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>'DSC_0467.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>DSC_0468.jpg</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>'DSC_0468.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>DSC_0469.jpg</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>'DSC_0469.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>DSC_0470.jpg</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>'DSC_0470.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>DSC_0471.jpg</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>'DSC_0471.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>DSC_0474.jpg</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>'DSC_0474.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>DSC_0475.jpg</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>'DSC_0475.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>DSC_0476.jpg</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>'DSC_0476.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>DSC_0477.jpg</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>'DSC_0477.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>DSC_0478.jpg</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>'DSC_0478.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>DSC_0479.jpg</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>'DSC_0479.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>DSC_0480.jpg</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>'DSC_0480.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>DSC_0481.jpg</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>'DSC_0481.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>DSC_0482.jpg</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>'DSC_0482.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>DSC_0483.jpg</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>'DSC_0483.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>DSC_0485.jpg</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>'DSC_0485.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>DSC_0486.jpg</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>'DSC_0486.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>DSC_0487.jpg</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>'DSC_0487.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>DSC_0489.jpg</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>'DSC_0489.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>DSC_0490.jpg</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>'DSC_0490.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>DSC_0491.jpg</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>'DSC_0491.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>DSC_0492.jpg</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>'DSC_0492.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>DSC_0493.jpg</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>'DSC_0493.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>DSC_0494.jpg</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>'DSC_0494.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>DSC_0495.jpg</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>'DSC_0495.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>DSC_0497.jpg</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>'DSC_0497.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>DSC_0499.jpg</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>'DSC_0499.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>DSC_0500.jpg</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>'DSC_0500.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>DSC_0501.jpg</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>'DSC_0501.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>DSC_0502.jpg</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>'DSC_0502.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>DSC_0503.jpg</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>'DSC_0503.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>DSC_0504.jpg</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>'DSC_0504.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>DSC_0505.jpg</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>'DSC_0505.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>DSC_0507.jpg</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>'DSC_0507.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>DSC_0508.jpg</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>'DSC_0508.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>DSC_0509.jpg</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>'DSC_0509.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>DSC_0510.jpg</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>'DSC_0510.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>DSC_0511.jpg</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>'DSC_0511.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>DSC_0512.jpg</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>'DSC_0512.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>DSC_0513.jpg</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>'DSC_0513.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>DSC_0514.jpg</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>'DSC_0514.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>DSC_0518.jpg</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>'DSC_0518.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>DSC_0519.jpg</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>'DSC_0519.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>DSC_0520.jpg</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>'DSC_0520.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>DSC_0521.jpg</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>'DSC_0521.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>DSC_0522.jpg</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>'DSC_0522.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>DSC_0523.jpg</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>'DSC_0523.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>DSC_0524.jpg</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>'DSC_0524.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>DSC_0525.jpg</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>'DSC_0525.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>DSC_0526.jpg</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>'DSC_0526.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>DSC_0527.jpg</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>'DSC_0527.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>DSC_0528.jpg</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>'DSC_0528.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>DSC_0529.jpg</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>'DSC_0529.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>DSC_0530.jpg</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>'DSC_0530.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>DSC_0531.jpg</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>'DSC_0531.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>DSC_0532.jpg</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>'DSC_0532.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>DSC_0533.jpg</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>'DSC_0533.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>DSC_0534.jpg</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>'DSC_0534.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>DSC_0535.jpg</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>'DSC_0535.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>DSC_0536.jpg</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>'DSC_0536.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>DSC_0537.jpg</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>'DSC_0537.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>DSC_0538.jpg</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>'DSC_0538.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>DSC_0539.jpg</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>'DSC_0539.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>DSC_0540.jpg</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>'DSC_0540.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>DSC_0541.jpg</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>'DSC_0541.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>DSC_0542.jpg</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>'DSC_0542.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>DSC_0543.jpg</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>'DSC_0543.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>DSC_0544.jpg</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>'DSC_0544.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>DSC_0545.jpg</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>'DSC_0545.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>DSC_0546.jpg</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>'DSC_0546.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>DSC_0547.jpg</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>'DSC_0547.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>DSC_0548.jpg</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>'DSC_0548.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>DSC_0549.jpg</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>'DSC_0549.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>DSC_0551.jpg</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>'DSC_0551.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>DSC_0552.jpg</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>'DSC_0552.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>DSC_0553.jpg</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>'DSC_0553.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>DSC_0554.jpg</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>'DSC_0554.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>DSC_0555.jpg</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>'DSC_0555.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>DSC_0556.jpg</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>'DSC_0556.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>DSC_0557.jpg</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>'DSC_0557.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>DSC_0558.jpg</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>'DSC_0558.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>DSC_0559.jpg</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>'DSC_0559.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>DSC_0561.jpg</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>'DSC_0561.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>DSC_0564.jpg</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>'DSC_0564.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>DSC_0565.jpg</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>'DSC_0565.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>DSC_0566.jpg</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>'DSC_0566.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>DSC_0567.jpg</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>'DSC_0567.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>DSC_0568.jpg</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>'DSC_0568.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>DSC_0569.jpg</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>'DSC_0569.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>DSC_0570.jpg</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>'DSC_0570.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>DSC_0571.jpg</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>'DSC_0571.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>DSC_0572.jpg</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>'DSC_0572.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>DSC_0573.jpg</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>'DSC_0573.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>DSC_0574.jpg</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>'DSC_0574.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>DSC_0575.jpg</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>'DSC_0575.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>DSC_0576.jpg</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>'DSC_0576.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>DSC_0577.jpg</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>'DSC_0577.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>DSC_0578.jpg</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>'DSC_0578.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>DSC_0579.jpg</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>'DSC_0579.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>DSC_0580.jpg</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>'DSC_0580.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>DSC_0581.jpg</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>'DSC_0581.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>DSC_0582.jpg</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>'DSC_0582.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>DSC_0583.jpg</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>'DSC_0583.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>DSC_0584.jpg</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>'DSC_0584.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>DSC_0585.jpg</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>'DSC_0585.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>DSC_0586.jpg</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>'DSC_0586.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>DSC_0587.jpg</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>'DSC_0587.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>DSC_0588.jpg</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>'DSC_0588.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>DSC_0589.jpg</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>'DSC_0589.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>DSC_0590.jpg</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>'DSC_0590.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>DSC_0591.jpg</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>'DSC_0591.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>DSC_0593.jpg</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>'DSC_0593.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>DSC_0594.jpg</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>'DSC_0594.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>DSC_0595.jpg</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>'DSC_0595.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>DSC_0596.jpg</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>'DSC_0596.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>DSC_0597.jpg</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>'DSC_0597.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>DSC_0598.jpg</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>'DSC_0598.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>DSC_0599.jpg</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>'DSC_0599.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>DSC_0600.jpg</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>'DSC_0600.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>DSC_0601.jpg</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>'DSC_0601.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>DSC_0602.jpg</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>'DSC_0602.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>DSC_0603.jpg</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>'DSC_0603.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>DSC_0604.jpg</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>'DSC_0604.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>DSC_0605.jpg</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>'DSC_0605.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>DSC_0606.jpg</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>'DSC_0606.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>DSC_0607.jpg</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>'DSC_0607.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>DSC_0608.jpg</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>'DSC_0608.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>DSC_0609.jpg</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>'DSC_0609.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>DSC_0612.jpg</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>'DSC_0612.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>DSC_0613.jpg</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>'DSC_0613.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>DSC_0614.jpg</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>'DSC_0614.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>DSC_0615.jpg</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>'DSC_0615.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>DSC_0617.jpg</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>'DSC_0617.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>DSC_0618.jpg</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>'DSC_0618.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>DSC_0619.jpg</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>'DSC_0619.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>DSC_0620.jpg</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>'DSC_0620.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>DSC_0621.jpg</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>'DSC_0621.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>DSC_0622.jpg</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>'DSC_0622.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>DSC_0623.jpg</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>'DSC_0623.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>DSC_0624.jpg</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>'DSC_0624.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>DSC_0625.jpg</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>'DSC_0625.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>DSC_0626.jpg</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>'DSC_0626.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>DSC_0627.jpg</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>'DSC_0627.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>DSC_0628.jpg</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>'DSC_0628.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>DSC_0631.jpg</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>'DSC_0631.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>DSC_0632.jpg</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>'DSC_0632.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>DSC_0633.jpg</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>'DSC_0633.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>DSC_0634.jpg</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>'DSC_0634.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>DSC_0635.jpg</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>'DSC_0635.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>DSC_0636.jpg</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>'DSC_0636.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>DSC_0637.jpg</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>'DSC_0637.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>DSC_0638.jpg</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>'DSC_0638.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>DSC_0639.jpg</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>'DSC_0639.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>DSC_0640.jpg</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>'DSC_0640.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>DSC_0641.jpg</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>'DSC_0641.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>DSC_0642.jpg</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>'DSC_0642.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>DSC_0643.jpg</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>'DSC_0643.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>DSC_0644.jpg</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>'DSC_0644.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>DSC_0645.jpg</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>'DSC_0645.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>DSC_0646.jpg</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>'DSC_0646.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>DSC_0647.jpg</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>'DSC_0647.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>DSC_0648.jpg</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>'DSC_0648.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>DSC_0649.jpg</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>'DSC_0649.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>DSC_0650.jpg</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>'DSC_0650.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>DSC_0651.jpg</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>'DSC_0651.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>DSC_0652.jpg</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>'DSC_0652.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>DSC_0653.jpg</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>'DSC_0653.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>DSC_0654.jpg</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>'DSC_0654.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>DSC_0655.jpg</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>'DSC_0655.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>DSC_0656.jpg</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>'DSC_0656.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>DSC_0657.jpg</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>'DSC_0657.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>DSC_0658.jpg</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>'DSC_0658.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>DSC_0660.jpg</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>'DSC_0660.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>DSC_0661.jpg</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>'DSC_0661.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>DSC_0662.jpg</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>'DSC_0662.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>DSC_0663.jpg</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>'DSC_0663.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>DSC_0664.jpg</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>'DSC_0664.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>DSC_0665.jpg</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>'DSC_0665.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>DSC_0666.jpg</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>'DSC_0666.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>DSC_0667.jpg</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>'DSC_0667.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>DSC_0668.jpg</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>'DSC_0668.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>DSC_0669.jpg</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>'DSC_0669.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>DSC_0670.jpg</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>'DSC_0670.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>DSC_0671.jpg</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>'DSC_0671.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>DSC_0672.jpg</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>'DSC_0672.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>DSC_0673.jpg</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>'DSC_0673.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>DSC_0674.jpg</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>'DSC_0674.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>DSC_0675.jpg</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>'DSC_0675.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>DSC_0676.jpg</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>'DSC_0676.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>DSC_0677.jpg</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>'DSC_0677.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>DSC_0679.jpg</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>'DSC_0679.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>DSC_0680.jpg</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>'DSC_0680.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>DSC_0681.jpg</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>'DSC_0681.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>DSC_0682.jpg</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>'DSC_0682.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>DSC_0683.jpg</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>'DSC_0683.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>DSC_0684.jpg</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>'DSC_0684.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>DSC_0685.jpg</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>'DSC_0685.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>DSC_0686.jpg</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>'DSC_0686.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>DSC_0687.jpg</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>'DSC_0687.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>DSC_0688.jpg</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>'DSC_0688.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>DSC_0689.jpg</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>'DSC_0689.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>DSC_0690.jpg</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>'DSC_0690.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>DSC_0691.jpg</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>'DSC_0691.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>DSC_0692.jpg</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>'DSC_0692.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>DSC_0693.jpg</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>'DSC_0693.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>DSC_0694.jpg</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>'DSC_0694.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>DSC_0696.jpg</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>'DSC_0696.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
           <t>DSC_0697.jpg</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr">
+      <c r="B600" t="inlineStr">
         <is>
           <t>'DSC_0697.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>DSC_0698.jpg</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>'DSC_0698.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>DSC_0699.jpg</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>'DSC_0699.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>DSC_0700.jpg</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>'DSC_0700.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>DSC_0701.jpg</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>'DSC_0701.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>DSC_0702.jpg</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>'DSC_0702.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>DSC_0703.jpg</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>'DSC_0703.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>DSC_0705.jpg</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>'DSC_0705.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>DSC_0706.jpg</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>'DSC_0706.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>DSC_0707.jpg</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>'DSC_0707.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>DSC_0708.jpg</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>'DSC_0708.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>DSC_0710.jpg</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>'DSC_0710.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>DSC_0711.jpg</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>'DSC_0711.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>DSC_0712.jpg</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>'DSC_0712.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>DSC_0713.jpg</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>'DSC_0713.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>DSC_0718.jpg</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>'DSC_0718.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>DSC_0719.jpg</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>'DSC_0719.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>DSC_0720.jpg</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>'DSC_0720.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>DSC_0721.jpg</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>'DSC_0721.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>DSC_0722.jpg</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>'DSC_0722.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>DSC_0723.jpg</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>'DSC_0723.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>DSC_0724.jpg</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>'DSC_0724.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>DSC_0725.jpg</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>'DSC_0725.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>DSC_0726.jpg</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>'DSC_0726.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>DSC_0727.jpg</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>'DSC_0727.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>DSC_0728.jpg</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>'DSC_0728.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>DSC_0729.jpg</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>'DSC_0729.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>DSC_0730.jpg</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>'DSC_0730.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>DSC_0731.jpg</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>'DSC_0731.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>DSC_0732.jpg</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>'DSC_0732.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>DSC_0733.jpg</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>'DSC_0733.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>DSC_0735.jpg</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>'DSC_0735.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>DSC_0736.jpg</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>'DSC_0736.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>DSC_0737.jpg</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>'DSC_0737.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>DSC_0738.jpg</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>'DSC_0738.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>DSC_0739.jpg</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>'DSC_0739.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>DSC_0740.jpg</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>'DSC_0740.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>DSC_0742.jpg</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>'DSC_0742.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>DSC_0743.jpg</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>'DSC_0743.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>DSC_0744.jpg</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>'DSC_0744.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>DSC_0745.jpg</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>'DSC_0745.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>DSC_0746.jpg</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>'DSC_0746.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>DSC_0747.jpg</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>'DSC_0747.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>DSC_0748.jpg</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>'DSC_0748.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>DSC_0749.jpg</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>'DSC_0749.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>DSC_0750.jpg</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>'DSC_0750.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>DSC_0752.jpg</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>'DSC_0752.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>DSC_0753.jpg</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>'DSC_0753.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>DSC_0754.jpg</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>'DSC_0754.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>DSC_0755.jpg</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>'DSC_0755.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>DSC_0756.jpg</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>'DSC_0756.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>DSC_0757.jpg</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>'DSC_0757.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>DSC_0758.jpg</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>'DSC_0758.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>DSC_0759.jpg</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>'DSC_0759.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>DSC_0760.jpg</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>'DSC_0760.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>DSC_0761.jpg</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>'DSC_0761.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>DSC_0762.jpg</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>'DSC_0762.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>DSC_0763.jpg</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>'DSC_0763.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>DSC_0764.jpg</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>'DSC_0764.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>DSC_0765.jpg</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>'DSC_0765.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>DSC_0766.jpg</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>'DSC_0766.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>DSC_0767.jpg</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>'DSC_0767.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>DSC_0768.jpg</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>'DSC_0768.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>DSC_0769.jpg</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>'DSC_0769.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>DSC_0770.jpg</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>'DSC_0770.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>DSC_0771.jpg</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>'DSC_0771.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>DSC_0772.jpg</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>'DSC_0772.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>DSC_0773.jpg</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>'DSC_0773.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>DSC_0774.jpg</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>'DSC_0774.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>DSC_0775.jpg</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>'DSC_0775.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>DSC_0776.jpg</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>'DSC_0776.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>DSC_0777.jpg</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>'DSC_0777.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>DSC_0778.jpg</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>'DSC_0778.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>DSC_0779.jpg</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>'DSC_0779.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>DSC_0780.jpg</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>'DSC_0780.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>DSC_0781.jpg</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>'DSC_0781.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>DSC_0782.jpg</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>'DSC_0782.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>DSC_0783.jpg</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>'DSC_0783.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>DSC_0784.jpg</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>'DSC_0784.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>DSC_0785.jpg</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>'DSC_0785.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>DSC_0786.jpg</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>'DSC_0786.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>DSC_0787.jpg</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>'DSC_0787.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>DSC_0788.jpg</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>'DSC_0788.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>DSC_0789.jpg</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>'DSC_0789.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>DSC_0803.jpg</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>'DSC_0803.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>DSC_0804.jpg</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>'DSC_0804.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>DSC_0805.jpg</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>'DSC_0805.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>DSC_0806.jpg</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>'DSC_0806.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>DSC_0807.jpg</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>'DSC_0807.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>DSC_0809.jpg</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>'DSC_0809.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>DSC_0810.jpg</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>'DSC_0810.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>DSC_0812.jpg</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>'DSC_0812.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>DSC_0813.jpg</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>'DSC_0813.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>DSC_0814.jpg</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>'DSC_0814.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>DSC_0815.jpg</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>'DSC_0815.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>DSC_0816.jpg</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>'DSC_0816.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>DSC_0817.jpg</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>'DSC_0817.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>DSC_0818.jpg</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>'DSC_0818.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>DSC_0819.jpg</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>'DSC_0819.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>DSC_0820.jpg</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>'DSC_0820.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>DSC_0821.jpg</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>'DSC_0821.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>DSC_0822.jpg</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>'DSC_0822.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>DSC_0823.jpg</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>'DSC_0823.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>DSC_0824.jpg</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>'DSC_0824.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>DSC_0825.jpg</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>'DSC_0825.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>DSC_0826.jpg</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>'DSC_0826.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>DSC_0827.jpg</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>'DSC_0827.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>DSC_0828.jpg</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>'DSC_0828.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>DSC_0829.jpg</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>'DSC_0829.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>DSC_0830.jpg</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>'DSC_0830.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>DSC_0832.jpg</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>'DSC_0832.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>DSC_0833.jpg</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>'DSC_0833.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>DSC_0834.jpg</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>'DSC_0834.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>DSC_0835.jpg</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>'DSC_0835.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>DSC_0836.jpg</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>'DSC_0836.jpg',</t>
         </is>
       </c>
     </row>

--- a/archivos_listados.xlsx
+++ b/archivos_listados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B46"/>
+  <dimension ref="A1:B201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,540 +443,2400 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DSC_0001.jpg</t>
+          <t>DSC_0031.jpg</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>'DSC_0001.jpg',</t>
+          <t>'DSC_0031.jpg',</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DSC_0002.jpg</t>
+          <t>DSC_0032.jpg</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>'DSC_0002.jpg',</t>
+          <t>'DSC_0032.jpg',</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DSC_0008.jpg</t>
+          <t>DSC_0033.jpg</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>'DSC_0008.jpg',</t>
+          <t>'DSC_0033.jpg',</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DSC_0009.jpg</t>
+          <t>DSC_0034.jpg</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>'DSC_0009.jpg',</t>
+          <t>'DSC_0034.jpg',</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DSC_0010.jpg</t>
+          <t>DSC_0035.jpg</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>'DSC_0010.jpg',</t>
+          <t>'DSC_0035.jpg',</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DSC_0011.jpg</t>
+          <t>DSC_0036.jpg</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>'DSC_0011.jpg',</t>
+          <t>'DSC_0036.jpg',</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DSC_0012.jpg</t>
+          <t>DSC_0037.jpg</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>'DSC_0012.jpg',</t>
+          <t>'DSC_0037.jpg',</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DSC_0013.jpg</t>
+          <t>DSC_0038.jpg</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>'DSC_0013.jpg',</t>
+          <t>'DSC_0038.jpg',</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DSC_0014.jpg</t>
+          <t>DSC_0039.jpg</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>'DSC_0014.jpg',</t>
+          <t>'DSC_0039.jpg',</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DSC_0015.jpg</t>
+          <t>DSC_0040.jpg</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>'DSC_0015.jpg',</t>
+          <t>'DSC_0040.jpg',</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DSC_0027.jpg</t>
+          <t>DSC_0041.jpg</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>'DSC_0027.jpg',</t>
+          <t>'DSC_0041.jpg',</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DSC_0028.jpg</t>
+          <t>DSC_0043.jpg</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>'DSC_0028.jpg',</t>
+          <t>'DSC_0043.jpg',</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DSC_0029.jpg</t>
+          <t>DSC_0044.jpg</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>'DSC_0029.jpg',</t>
+          <t>'DSC_0044.jpg',</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DSC_0030.jpg</t>
+          <t>DSC_0045.jpg</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>'DSC_0030.jpg',</t>
+          <t>'DSC_0045.jpg',</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DSC_0063.jpg</t>
+          <t>DSC_0046.jpg</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>'DSC_0063.jpg',</t>
+          <t>'DSC_0046.jpg',</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DSC_0073.jpg</t>
+          <t>DSC_0050.jpg</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>'DSC_0073.jpg',</t>
+          <t>'DSC_0050.jpg',</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DSC_0078.jpg</t>
+          <t>DSC_0051.jpg</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>'DSC_0078.jpg',</t>
+          <t>'DSC_0051.jpg',</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DSC_0079.jpg</t>
+          <t>DSC_0052.jpg</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>'DSC_0079.jpg',</t>
+          <t>'DSC_0052.jpg',</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DSC_0087.jpg</t>
+          <t>DSC_0053.jpg</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>'DSC_0087.jpg',</t>
+          <t>'DSC_0053.jpg',</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DSC_0088.jpg</t>
+          <t>DSC_0054.jpg</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>'DSC_0088.jpg',</t>
+          <t>'DSC_0054.jpg',</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DSC_0098.jpg</t>
+          <t>DSC_0055.jpg</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>'DSC_0098.jpg',</t>
+          <t>'DSC_0055.jpg',</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DSC_0099.jpg</t>
+          <t>DSC_0056.jpg</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>'DSC_0099.jpg',</t>
+          <t>'DSC_0056.jpg',</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DSC_0100.jpg</t>
+          <t>DSC_0057.jpg</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>'DSC_0100.jpg',</t>
+          <t>'DSC_0057.jpg',</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DSC_0126.jpg</t>
+          <t>DSC_0060.jpg</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>'DSC_0126.jpg',</t>
+          <t>'DSC_0060.jpg',</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DSC_0127.jpg</t>
+          <t>DSC_0064.jpg</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>'DSC_0127.jpg',</t>
+          <t>'DSC_0064.jpg',</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DSC_0128.jpg</t>
+          <t>DSC_0065.jpg</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>'DSC_0128.jpg',</t>
+          <t>'DSC_0065.jpg',</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DSC_0137.jpg</t>
+          <t>DSC_0066.jpg</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>'DSC_0137.jpg',</t>
+          <t>'DSC_0066.jpg',</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DSC_0138.jpg</t>
+          <t>DSC_0071.jpg</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>'DSC_0138.jpg',</t>
+          <t>'DSC_0071.jpg',</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DSC_0142.jpg</t>
+          <t>DSC_0072.jpg</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>'DSC_0142.jpg',</t>
+          <t>'DSC_0072.jpg',</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DSC_0143.jpg</t>
+          <t>DSC_0074.jpg</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>'DSC_0143.jpg',</t>
+          <t>'DSC_0074.jpg',</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DSC_0144.jpg</t>
+          <t>DSC_0080.jpg</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>'DSC_0144.jpg',</t>
+          <t>'DSC_0080.jpg',</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DSC_0145.jpg</t>
+          <t>DSC_0081.jpg</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>'DSC_0145.jpg',</t>
+          <t>'DSC_0081.jpg',</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DSC_0150.jpg</t>
+          <t>DSC_0084.jpg</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>'DSC_0150.jpg',</t>
+          <t>'DSC_0084.jpg',</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DSC_0151.jpg</t>
+          <t>DSC_0085.jpg</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>'DSC_0151.jpg',</t>
+          <t>'DSC_0085.jpg',</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DSC_0152.jpg</t>
+          <t>DSC_0086.jpg</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>'DSC_0152.jpg',</t>
+          <t>'DSC_0086.jpg',</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DSC_0153.jpg</t>
+          <t>DSC_0101.jpg</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>'DSC_0153.jpg',</t>
+          <t>'DSC_0101.jpg',</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DSC_0154.jpg</t>
+          <t>DSC_0102.jpg</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>'DSC_0154.jpg',</t>
+          <t>'DSC_0102.jpg',</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DSC_0155.jpg</t>
+          <t>DSC_0103.jpg</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>'DSC_0155.jpg',</t>
+          <t>'DSC_0103.jpg',</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DSC_0156.jpg</t>
+          <t>DSC_0105.jpg</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>'DSC_0156.jpg',</t>
+          <t>'DSC_0105.jpg',</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DSC_0157.jpg</t>
+          <t>DSC_0106.jpg</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>'DSC_0157.jpg',</t>
+          <t>'DSC_0106.jpg',</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DSC_0158.jpg</t>
+          <t>DSC_0108.jpg</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>'DSC_0158.jpg',</t>
+          <t>'DSC_0108.jpg',</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DSC_0159.jpg</t>
+          <t>DSC_0109.jpg</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>'DSC_0159.jpg',</t>
+          <t>'DSC_0109.jpg',</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DSC_0160.jpg</t>
+          <t>DSC_0111.jpg</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>'DSC_0160.jpg',</t>
+          <t>'DSC_0111.jpg',</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DSC_0161.jpg</t>
+          <t>DSC_0113.jpg</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>'DSC_0161.jpg',</t>
+          <t>'DSC_0113.jpg',</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DSC_0162.jpg</t>
+          <t>DSC_0120.jpg</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>'DSC_0162.jpg',</t>
+          <t>'DSC_0120.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>DSC_0121.jpg</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>'DSC_0121.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>DSC_0123.jpg</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>'DSC_0123.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>DSC_0124.jpg</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>'DSC_0124.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>DSC_0139.jpg</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>'DSC_0139.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>DSC_0140.jpg</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>'DSC_0140.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>DSC_0141.jpg</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>'DSC_0141.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>DSC_0164.jpg</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>'DSC_0164.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>DSC_0165.jpg</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>'DSC_0165.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>DSC_0166.jpg</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>'DSC_0166.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>DSC_0167.jpg</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>'DSC_0167.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>DSC_0168.jpg</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>'DSC_0168.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>DSC_0169.jpg</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>'DSC_0169.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>DSC_0170.jpg</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>'DSC_0170.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>DSC_0171.jpg</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>'DSC_0171.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>DSC_0172.jpg</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>'DSC_0172.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>DSC_0173.jpg</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>'DSC_0173.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>DSC_0174.jpg</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>'DSC_0174.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>DSC_0175.jpg</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>'DSC_0175.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>DSC_0176.jpg</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>'DSC_0176.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>DSC_0177.jpg</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>'DSC_0177.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>DSC_0178.jpg</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>'DSC_0178.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>DSC_0179.jpg</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>'DSC_0179.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>DSC_0180.jpg</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>'DSC_0180.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>DSC_0181.jpg</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>'DSC_0181.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>DSC_0182.jpg</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>'DSC_0182.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>DSC_0183.jpg</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>'DSC_0183.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>DSC_0184.jpg</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>'DSC_0184.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>DSC_0185.jpg</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>'DSC_0185.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>DSC_0187.jpg</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>'DSC_0187.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>DSC_0188.jpg</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>'DSC_0188.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>DSC_0190.jpg</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>'DSC_0190.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>DSC_0191.jpg</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>'DSC_0191.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>DSC_0193.jpg</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>'DSC_0193.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>DSC_0252.jpg</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>'DSC_0252.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>DSC_0253.jpg</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>'DSC_0253.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>DSC_0254.jpg</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>'DSC_0254.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>DSC_0255.jpg</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>'DSC_0255.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>DSC_0256.jpg</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>'DSC_0256.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>DSC_0257.jpg</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>'DSC_0257.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>DSC_0258.jpg</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>'DSC_0258.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>DSC_0259.jpg</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>'DSC_0259.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>DSC_0260.jpg</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>'DSC_0260.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>DSC_0262.jpg</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>'DSC_0262.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>DSC_0263.jpg</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>'DSC_0263.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>DSC_0264.jpg</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>'DSC_0264.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>DSC_0265.jpg</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>'DSC_0265.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>DSC_0266.jpg</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>'DSC_0266.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>DSC_0267.jpg</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>'DSC_0267.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>DSC_0268.jpg</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>'DSC_0268.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>DSC_0269.jpg</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>'DSC_0269.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>DSC_0270.jpg</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>'DSC_0270.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>DSC_0271.jpg</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>'DSC_0271.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>DSC_0272.jpg</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>'DSC_0272.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>DSC_0273.jpg</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>'DSC_0273.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>DSC_0274.jpg</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>'DSC_0274.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>DSC_0275.jpg</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>'DSC_0275.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>DSC_0276.jpg</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>'DSC_0276.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>DSC_0277.jpg</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>'DSC_0277.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>DSC_0278.jpg</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>'DSC_0278.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>DSC_0281.jpg</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>'DSC_0281.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>DSC_0285.jpg</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>'DSC_0285.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>DSC_0286.jpg</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>'DSC_0286.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>DSC_0287.jpg</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>'DSC_0287.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>DSC_0288.jpg</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>'DSC_0288.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>DSC_0289.jpg</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>'DSC_0289.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>DSC_0290.jpg</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>'DSC_0290.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>DSC_0291.jpg</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>'DSC_0291.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>DSC_0292.jpg</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>'DSC_0292.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>DSC_0293.jpg</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>'DSC_0293.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>DSC_0294.jpg</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>'DSC_0294.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>DSC_0295.jpg</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>'DSC_0295.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>DSC_0296.jpg</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>'DSC_0296.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>DSC_0297.jpg</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>'DSC_0297.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>DSC_0298.jpg</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>'DSC_0298.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>DSC_0299.jpg</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>'DSC_0299.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>DSC_0301.jpg</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>'DSC_0301.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>DSC_0302.jpg</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>'DSC_0302.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>DSC_0303.jpg</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>'DSC_0303.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>DSC_0304.jpg</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>'DSC_0304.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>DSC_0306.jpg</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>'DSC_0306.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>DSC_0307.jpg</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>'DSC_0307.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>DSC_0308.jpg</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>'DSC_0308.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>DSC_0310.jpg</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>'DSC_0310.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>DSC_0311.jpg</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>'DSC_0311.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>DSC_0312.jpg</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>'DSC_0312.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>DSC_0313.jpg</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>'DSC_0313.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>DSC_0314.jpg</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>'DSC_0314.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>DSC_0315.jpg</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>'DSC_0315.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>DSC_0316.jpg</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>'DSC_0316.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>DSC_0318.jpg</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>'DSC_0318.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>DSC_0319.jpg</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>'DSC_0319.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>DSC_0320.jpg</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>'DSC_0320.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>DSC_0321.jpg</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>'DSC_0321.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>DSC_0322.jpg</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>'DSC_0322.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>DSC_0323.jpg</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>'DSC_0323.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>DSC_0324.jpg</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>'DSC_0324.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>DSC_0325.jpg</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>'DSC_0325.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>DSC_0326.jpg</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>'DSC_0326.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>DSC_0327.jpg</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>'DSC_0327.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>DSC_0328.jpg</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>'DSC_0328.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>DSC_0330.jpg</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>'DSC_0330.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>DSC_0331.jpg</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>'DSC_0331.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>DSC_0332.jpg</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>'DSC_0332.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>DSC_0333.jpg</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>'DSC_0333.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>DSC_0334.jpg</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>'DSC_0334.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>DSC_0335.jpg</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>'DSC_0335.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>DSC_0336.jpg</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>'DSC_0336.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>DSC_0338.jpg</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>'DSC_0338.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>DSC_0339.jpg</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>'DSC_0339.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>DSC_0340.jpg</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>'DSC_0340.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>DSC_0341.jpg</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>'DSC_0341.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>DSC_0342.jpg</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>'DSC_0342.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>DSC_0343.jpg</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>'DSC_0343.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>DSC_0344.jpg</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>'DSC_0344.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>DSC_0346.jpg</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>'DSC_0346.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>DSC_0348.jpg</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>'DSC_0348.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>DSC_0349.jpg</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>'DSC_0349.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>DSC_0354.jpg</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>'DSC_0354.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>DSC_0356.jpg</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>'DSC_0356.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>DSC_0357.jpg</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>'DSC_0357.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>DSC_0360.jpg</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>'DSC_0360.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>DSC_0361.jpg</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>'DSC_0361.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>DSC_0362.jpg</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>'DSC_0362.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>DSC_0363.jpg</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>'DSC_0363.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>DSC_0364.jpg</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>'DSC_0364.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>DSC_0367.jpg</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>'DSC_0367.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>DSC_0368.jpg</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>'DSC_0368.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>DSC_0369.jpg</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>'DSC_0369.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>DSC_0370.jpg</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>'DSC_0370.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>DSC_0372.jpg</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>'DSC_0372.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>DSC_0373.jpg</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>'DSC_0373.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>DSC_0374.jpg</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>'DSC_0374.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>DSC_0375.jpg</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>'DSC_0375.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>DSC_0377.jpg</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>'DSC_0377.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>DSC_0378.jpg</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>'DSC_0378.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>DSC_0381.jpg</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>'DSC_0381.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>DSC_0383.jpg</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>'DSC_0383.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>DSC_0384.jpg</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>'DSC_0384.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>DSC_0385.jpg</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>'DSC_0385.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>DSC_0388.jpg</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>'DSC_0388.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>DSC_0389.jpg</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>'DSC_0389.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>DSC_0390.jpg</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>'DSC_0390.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>DSC_0391.jpg</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>'DSC_0391.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>DSC_0392.jpg</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>'DSC_0392.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>DSC_0394.jpg</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>'DSC_0394.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>DSC_0396.jpg</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>'DSC_0396.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>DSC_0404.jpg</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>'DSC_0404.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>DSC_0405.jpg</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>'DSC_0405.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>DSC_0407.jpg</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>'DSC_0407.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>DSC_0408.jpg</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>'DSC_0408.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>DSC_0409.jpg</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>'DSC_0409.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>DSC_0412.jpg</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>'DSC_0412.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>DSC_0413.jpg</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>'DSC_0413.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>DSC_0415.jpg</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>'DSC_0415.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>DSC_0416.jpg</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>'DSC_0416.jpg',</t>
         </is>
       </c>
     </row>
